--- a/docs/analysis/pokrytie-maskirovaniya-perechen-d8.xlsx
+++ b/docs/analysis/pokrytie-maskirovaniya-perechen-d8.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,12 +51,23 @@
     </font>
     <font>
       <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="002B4C8C"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="001E7A4C"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00AAAAAA"/>
       <sz val="9"/>
     </font>
     <font>
@@ -99,7 +110,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -114,6 +125,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FBE7E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDF2FB"/>
       </patternFill>
     </fill>
     <fill>
@@ -153,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -164,40 +180,46 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -565,15 +587,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -583,10 +606,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="48" customHeight="1">
+    <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Источник требований: Приложение №2 к приказу Генерального директора АО «Инвестиционная компания Д8» от 18.05.2026 № 26-18/05-1. Нумерация пунктов — как в оригинальном документе (подпункты без сквозной нумерации в исходнике перечислены как отдельные строки одного пункта). Статус «Маскируется» — покрыто встроенным типом PIIType платформы. «Частично» — тип есть, но формулировка заказчика шире. «Не маскируется» — вне скоупа PII-маскировщика (организационная/финансовая/IT-информация, не именованная сущность).</t>
+          <t>Источник требований: Приложение №2 к приказу Генерального директора АО «Инвестиционная компания Д8» от 18.05.2026 № 26-18/05-1. Нумерация пунктов — как в оригинальном документе (подпункты без сквозной нумерации в исходнике перечислены как отдельные строки одного пункта). Статус «Маскируется» — покрыто встроенным типом PIIType платформы. «Частично» — тип есть, но формулировка заказчика шире. «Не маскируется» — вне скоупа PII-маскировщика (организационная/финансовая/IT-информация, не именованная сущность). Для строк со статусом «Не маскируется» в столбце G — вопрос к заказчику с примером, чтобы уточнить, что конкретно ожидается маскировать по этому пункту.</t>
         </is>
       </c>
     </row>
@@ -621,6 +644,11 @@
           <t>Комментарий</t>
         </is>
       </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Вопрос к заказчику (для уточнения объёма маскирования)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -653,6 +681,11 @@
           <t>Организационная информация, не PII-сущность</t>
         </is>
       </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Пример: «Обслуживание по индивидуальному тарифному плану с персональным менеджером Ивановым И.И.». Что именно маскировать: описание условий схемы целиком (текст) или только упоминания сотрудников/клиентов в нём (уже покрывается ФИО)?</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -675,7 +708,7 @@
           <t>PERSON / FULL_NAME</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Маскируется</t>
         </is>
@@ -683,6 +716,11 @@
       <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Прямое совпадение со встроенным типом</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -707,7 +745,7 @@
           <t>PASSPORT</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>Частично</t>
         </is>
@@ -715,6 +753,11 @@
       <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Встроен только паспорт РФ; иные виды документов — нет</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -739,7 +782,7 @@
           <t>ADDRESS</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>Маскируется</t>
         </is>
@@ -747,6 +790,11 @@
       <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Прямое совпадение со встроенным типом</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -771,7 +819,7 @@
           <t>PHONE</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>Маскируется</t>
         </is>
@@ -779,6 +827,11 @@
       <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Прямое совпадение со встроенным типом</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -803,7 +856,7 @@
           <t>EMAIL</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>Маскируется</t>
         </is>
@@ -811,6 +864,11 @@
       <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Прямое совпадение со встроенным типом</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -835,7 +893,7 @@
           <t>PERSON (частично)</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>Частично</t>
         </is>
@@ -843,6 +901,11 @@
       <c r="F11" s="5" t="inlineStr">
         <is>
           <t>ФИО таких лиц распознаётся, но сама роль/связь («выгодоприобретатель», «бенефициар») — не отдельная сущность</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -867,7 +930,7 @@
           <t>PERSON / ORG (частично)</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>Частично</t>
         </is>
@@ -875,6 +938,11 @@
       <c r="F12" s="5" t="inlineStr">
         <is>
           <t>ФИО/наименование — да; внутренний уникальный код клиента — нет типа</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -909,6 +977,11 @@
           <t>Известный пробел: «Номер договора» не входит во встроенные типы, нужен кастомный тип</t>
         </is>
       </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Пример: «Договор № ИС-2024/0817 от 12.03.2024». Нужен ли отдельный кастомный тип «НОМЕР_ДОГОВОРА» для номера и даты, или достаточно маскирования ФИО/сумм, упомянутых рядом в тексте?</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -941,6 +1014,11 @@
           <t>Номер счёта отдельно распознаётся (BANK_ACCOUNT), но содержание сделки — нет</t>
         </is>
       </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Пример: «По счёту № 40817810900000012345 клиента Иванова И.И. 15.03.2024 совершена сделка на покупку 100 акций Сбербанк на сумму 25 000 руб.». Номер счёта и ФИО уже маскируются — нужно ли дополнительно маскировать содержание сделки (актив, объём, сумму) как отдельную категорию?</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -973,6 +1051,11 @@
           <t>Финансово-операционные данные, не именованная сущность</t>
         </is>
       </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Пример: «Клиенту Петрову П.П. предоставлен маржинальный заём в размере 500 000 руб. под 12% годовых». Маскировать ли сумму и условия займа отдельно от ФИО клиента (которое уже маскируется)?</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1005,6 +1088,11 @@
           <t>Финансово-операционные данные, не именованная сущность</t>
         </is>
       </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Пример: «Задолженность клиента Сидорова С.С. по состоянию на 01.04.2024 составляет 150 000 руб.». Требуется ли маскировать сумму задолженности как отдельную категорию, или достаточно маскирования ФИО?</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1037,6 +1125,11 @@
           <t>Финансово-операционные данные, не именованная сущность</t>
         </is>
       </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Пример: «Обязательство по сделке № 145 от 10.01.2024 признано прекращённым 20.02.2024 в связи с неисполнением». Что здесь требует маскирования: номер сделки, сам факт прекращения, обе части?</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1069,6 +1162,11 @@
           <t>Финансово-операционные данные, не именованная сущность</t>
         </is>
       </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Пример: «Исходящий остаток по счёту клиента: 500 акций Газпром, плановый остаток на конец периода — 480 акций». Считаются ли такие цифры конфиденциальными сами по себе (без ФИО в той же фразе), и если да — нужен отдельный тип?</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1101,6 +1199,11 @@
           <t>Документ целиком; вложенные ФИО/суммы распознаются отдельно, но не как категория</t>
         </is>
       </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Пример: «Поручение клиента Кузнецова К.К. на покупку 200 облигаций ОФЗ-26238 на сумму 210 000 руб.». Маскировать ли поручение как документ целиком, или только вложенные ФИО/суммы (уже покрыты существующими типами)?</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1133,6 +1236,11 @@
           <t>Аналогично п. 1.4</t>
         </is>
       </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Пример: «Поручение на продажу 10 000 USD по курсу 92,50». Аналогично п. 1.4: маскировать текст поручения целиком или только сумму/курс как отдельную категорию?</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1155,7 +1263,7 @@
           <t>ORG (частично)</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>Частично</t>
         </is>
@@ -1163,6 +1271,11 @@
       <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Название юрлица распознаётся, но сама информация о взаимоотношениях — нет</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1197,6 +1310,11 @@
           <t>Договорная информация, не PII-сущность</t>
         </is>
       </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>Пример: «По агентскому соглашению с ООО «Брокер-Партнёр» комиссия составляет 0,15% от объёма сделок клиентов, привлечённых партнёром». Считаются ли условия соглашения (ставка, объём) данными для маскирования, или это регулируется NDA/договором вне PII-маскировщика?</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1229,6 +1347,11 @@
           <t>IT-инфраструктура, вне скоупа PII-маскировщика</t>
         </is>
       </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Пример: «Доступ к модулю «Клиентские счета» имеют роли: Операционист, Старший операционист, Руководитель отдела». Подтвердите: этот пункт закрывается организационными/техническими мерами (RBAC, журналирование доступа), а не PII-маскировщиком?</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -1261,6 +1384,11 @@
           <t>IT-инфраструктура, вне скоупа PII-маскировщика</t>
         </is>
       </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Пример: «Сотруднику Смирнову А.А. предоставлен доступ уровня «Администратор» к CRM». ФИО сотрудника уже маскируется — нужно ли отдельно маскировать сам факт/уровень предоставленных прав доступа?</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -1293,6 +1421,11 @@
           <t>IT-инфраструктура, вне скоупа PII-маскировщика</t>
         </is>
       </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Пример: «Схема сети: DMZ 10.10.1.0/24 → firewall → внутренний сегмент 10.10.2.0/24, сервер itq-db-01». Нужен ли отдельный тип для IP-адресов/имён серверов (сейчас не входит во встроенные типы)?</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -1325,6 +1458,11 @@
           <t>Исходный код, вне скоупа PII-маскировщика</t>
         </is>
       </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>Пример: фрагмент внутреннего скрипта расчёта комиссии, вставленный в чат с ИИ. Требуется построчное маскирование кода, или предполагается полный запрет на передачу кода в ИИ (политика уровня п. 5.1) без частичного маскирования?</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -1357,6 +1495,11 @@
           <t>Организационно-техническая ИБ-информация</t>
         </is>
       </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>Пример: «Используется двухфакторная аутентификация и шифрование AES-256 для хранения данных клиентов». Считать ли названия методов/технологий защиты данными для маскирования, или контроль обеспечивается запретом передачи таких документов в ИИ?</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -1389,6 +1532,11 @@
           <t>Организационно-техническая ИБ-информация</t>
         </is>
       </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>Пример: «Сотрудники проходят проверку службой безопасности и подписывают NDA сроком на 3 года». Маскировать ли описание процедур, или только ФИО упомянутых сотрудников (уже покрывается)?</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -1421,6 +1569,11 @@
           <t>Организационно-техническая ИБ-информация</t>
         </is>
       </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Пример: «Резервный дата-центр расположен по адресу [адрес], время переключения — 15 минут». Маскировать ли адрес объекта (тип ADDRESS настроен на адреса физлиц, не гарантированно сработает на адрес ЦОД) и технические параметры?</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -1453,6 +1606,11 @@
           <t>Организационно-техническая ИБ-информация</t>
         </is>
       </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>Пример: «Установлена система видеонаблюдения Hikvision DS-2CD2, СКУД Perco». Нужно ли маскировать названия/модели используемых средств защиты как отдельную категорию?</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -1485,6 +1643,11 @@
           <t>Организационно-техническая ИБ-информация</t>
         </is>
       </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>Пример: «Пропускной режим: турникеты на 1 этаже, пост охраны круглосуточно, видеонаблюдение периметра». Считается ли такое описание конфиденциальным для маскирования в документах, обрабатываемых ИИ?</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -1517,6 +1680,11 @@
           <t>Организационно-техническая ИБ-информация</t>
         </is>
       </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>Пример: «По итогам пентеста в марте 2024 выявлено 3 уязвимости критического уровня в модуле авторизации». Маскировать ли содержание отчёта (находки, уязвимости) как отдельную категорию, или предполагается полный запрет на загрузку таких отчётов в систему?</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -1549,6 +1717,11 @@
           <t>Зонтичная политика («не отправлять в ИИ сведения из разделов 1–4»), не отдельный тип данных</t>
         </is>
       </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>Пример: сотрудник загружает в чат с ИИ выписку по счёту клиента для анализа. Как должна работать проверка: блокировка загрузки документа целиком при обнаружении данных из разделов 1–4, или маскирование конкретных полей перед отправкой в модель?</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -1581,11 +1754,16 @@
           <t>Зонтичная политика, не отдельный тип данных</t>
         </is>
       </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>Пример: ИИ в ответе процитировал фрагмент загруженного договора с ФИО и суммой. Должен ли ответ агента дополнительно проверяться/маскироваться перед показом пользователю, аналогично входящим документам?</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1606,85 +1784,85 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>СВОДКА ПО СТАТУСАМ</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Количество пунктов</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>Доля</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Маскируется</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n">
+      <c r="B4" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="15">
         <f>B4/30</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Частично</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="15">
         <f>B5/30</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>Не маскируется</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="n">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>Не маскируется</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
         <v>22</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="15">
         <f>B6/30</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>Итого пунктов</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="18" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="9" ht="50" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>Пункты «Не маскируется» — это преимущественно разделы 2–5 Перечня (контрагенты, IT-инфраструктура, ИБ-меры, политика работы с ИИ) и часть раздела 1 (номера договоров, финансово-операционные детали) — они не являются именованными PII-сущностями и требуют либо кастомных типов, либо контроля на уровне разграничения доступа/DLP, а не PII-маскирования.</t>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>Пункты «Не маскируется» — это преимущественно разделы 2–5 Перечня (контрагенты, IT-инфраструктура, ИБ-меры, политика работы с ИИ) и часть раздела 1 (номера договоров, финансово-операционные детали) — они не являются именованными PII-сущностями и требуют либо кастомных типов, либо контроля на уровне разграничения доступа/DLP, а не PII-маскирования. По каждому такому пункту в столбце «Вопрос к заказчику» на листе «Покрытие маскирования» сформулирован уточняющий вопрос с примером — ответы заказчика нужны, чтобы решить, где достаточно организационных/DLP-мер, а где требуется разработка кастомного PIIType.</t>
         </is>
       </c>
     </row>

--- a/docs/analysis/pokrytie-maskirovaniya-perechen-d8.xlsx
+++ b/docs/analysis/pokrytie-maskirovaniya-perechen-d8.xlsx
@@ -57,17 +57,17 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="00AAAAAA"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="001E7A4C"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00AAAAAA"/>
       <sz val="9"/>
     </font>
     <font>
@@ -169,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -180,10 +180,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -192,10 +192,16 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -587,16 +593,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -606,10 +614,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="76" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Источник требований: Приложение №2 к приказу Генерального директора АО «Инвестиционная компания Д8» от 18.05.2026 № 26-18/05-1. Нумерация пунктов — как в оригинальном документе (подпункты без сквозной нумерации в исходнике перечислены как отдельные строки одного пункта). Статус «Маскируется» — покрыто встроенным типом PIIType платформы. «Частично» — тип есть, но формулировка заказчика шире. «Не маскируется» — вне скоупа PII-маскировщика (организационная/финансовая/IT-информация, не именованная сущность). Для строк со статусом «Не маскируется» в столбце G — вопрос к заказчику с примером, чтобы уточнить, что конкретно ожидается маскировать по этому пункту.</t>
+          <t>Источник требований: Приложение №2 к приказу Генерального директора АО «Инвестиционная компания Д8» от 18.05.2026 № 26-18/05-1. Нумерация пунктов — как в оригинальном документе (подпункты без сквозной нумерации в исходнике перечислены как отдельные строки одного пункта). Статус «Маскируется» — покрыто встроенным типом PIIType платформы. «Частично» — тип есть, но формулировка заказчика шире. «Не маскируется» — вне скоупа PII-маскировщика (организационная/финансовая/IT-информация, не именованная сущность). Столбец F — краткий флаг: нужно ли уточнение объёма у заказчика (Да — для всех «Не маскируется», где полностью неясно, что относится к пункту). Столбец H — сам вопрос с примером. Столбец I — какие из уже готовых тестовых документов (docs/test-data/anonymizer-2-test-documents/, ground truth в manifest.json) можно использовать, чтобы прогнать и проверить маскирование по этому пункту; «—» значит, что подходящего документа в наборе пока нет и потребуется отдельный тестовый файл.</t>
         </is>
       </c>
     </row>
@@ -641,12 +649,22 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
+          <t>Требуется уточнение, что именно маскировать</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
           <t>Комментарий</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Вопрос к заказчику (для уточнения объёма маскирования)</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Название эталонных файлов для проверки маскирования</t>
         </is>
       </c>
     </row>
@@ -676,14 +694,24 @@
           <t>Не маскируется</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Организационная информация, не PII-сущность</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>Пример: «Обслуживание по индивидуальному тарифному плану с персональным менеджером Ивановым И.И.». Что именно маскировать: описание условий схемы целиком (текст) или только упоминания сотрудников/клиентов в нём (уже покрывается ФИО)?</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>— (нет соответствующей сущности в текущем наборе)</t>
         </is>
       </c>
     </row>
@@ -708,19 +736,29 @@
           <t>PERSON / FULL_NAME</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Маскируется</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Прямое совпадение со встроенным типом</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>01-anketa-klienta, 02-sluzhebnaya-zapiska, 03-reestr-operaciy (все форматы; см. manifest.json, тип «ФИО»)</t>
         </is>
       </c>
     </row>
@@ -745,19 +783,29 @@
           <t>PASSPORT</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Частично</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Встроен только паспорт РФ; иные виды документов — нет</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>01-anketa-klienta (поля «Паспорт (серия+номер)», «Место выдачи паспорта»)</t>
         </is>
       </c>
     </row>
@@ -782,19 +830,29 @@
           <t>ADDRESS</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Маскируется</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Прямое совпадение со встроенным типом</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>01-anketa-klienta, 02-sluzhebnaya-zapiska (тип «Адрес»)</t>
         </is>
       </c>
     </row>
@@ -819,19 +877,29 @@
           <t>PHONE</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>Маскируется</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Прямое совпадение со встроенным типом</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>01-anketa-klienta, 02-sluzhebnaya-zapiska, 03-reestr-operaciy (тип «Телефон»)</t>
         </is>
       </c>
     </row>
@@ -856,19 +924,29 @@
           <t>EMAIL</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>Маскируется</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Прямое совпадение со встроенным типом</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>01-anketa-klienta, 02-sluzhebnaya-zapiska (тип «Email»)</t>
         </is>
       </c>
     </row>
@@ -893,19 +971,29 @@
           <t>PERSON (частично)</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Частично</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>ФИО таких лиц распознаётся, но сама роль/связь («выгодоприобретатель», «бенефициар») — не отдельная сущность</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>— (роль/связь как отдельная сущность в наборе не смоделирована; ФИО — см. п. 1.2 выше)</t>
         </is>
       </c>
     </row>
@@ -930,19 +1018,29 @@
           <t>PERSON / ORG (частично)</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>Частично</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>ФИО/наименование — да; внутренний уникальный код клиента — нет типа</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
+        <is>
+          <t>01-anketa-klienta, 02-sluzhebnaya-zapiska, 03-reestr-operaciy (только ФИО; уникальный код клиента в наборе не смоделирован)</t>
         </is>
       </c>
     </row>
@@ -972,14 +1070,24 @@
           <t>Не маскируется</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Известный пробел: «Номер договора» не входит во встроенные типы, нужен кастомный тип</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>Пример: «Договор № ИС-2024/0817 от 12.03.2024». Нужен ли отдельный кастомный тип «НОМЕР_ДОГОВОРА» для номера и даты, или достаточно маскирования ФИО/сумм, упомянутых рядом в тексте?</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>01-anketa-klienta, 02-sluzhebnaya-zapiska, 03-reestr-operaciy (поле «Номер договора»; отдельная «дата договора» в наборе не смоделирована)</t>
         </is>
       </c>
     </row>
@@ -1009,14 +1117,24 @@
           <t>Не маскируется</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Номер счёта отдельно распознаётся (BANK_ACCOUNT), но содержание сделки — нет</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>Пример: «По счёту № 40817810900000012345 клиента Иванова И.И. 15.03.2024 совершена сделка на покупку 100 акций Сбербанк на сумму 25 000 руб.». Номер счёта и ФИО уже маскируются — нужно ли дополнительно маскировать содержание сделки (актив, объём, сумму) как отдельную категорию?</t>
+        </is>
+      </c>
+      <c r="I14" s="11" t="inlineStr">
+        <is>
+          <t>02-sluzhebnaya-zapiska (поля «Сумма операции», «Дата операции»), 03-reestr-operaciy (реестр из 5 операций)</t>
         </is>
       </c>
     </row>
@@ -1046,14 +1164,24 @@
           <t>Не маскируется</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Финансово-операционные данные, не именованная сущность</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>Пример: «Клиенту Петрову П.П. предоставлен маржинальный заём в размере 500 000 руб. под 12% годовых». Маскировать ли сумму и условия займа отдельно от ФИО клиента (которое уже маскируется)?</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>— (нет соответствующей сущности в текущем наборе, нужен отдельный документ)</t>
         </is>
       </c>
     </row>
@@ -1083,14 +1211,24 @@
           <t>Не маскируется</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>Финансово-операционные данные, не именованная сущность</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>Пример: «Задолженность клиента Сидорова С.С. по состоянию на 01.04.2024 составляет 150 000 руб.». Требуется ли маскировать сумму задолженности как отдельную категорию, или достаточно маскирования ФИО?</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>— (нет соответствующей сущности в текущем наборе, нужен отдельный документ)</t>
         </is>
       </c>
     </row>
@@ -1120,14 +1258,24 @@
           <t>Не маскируется</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Финансово-операционные данные, не именованная сущность</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>Пример: «Обязательство по сделке № 145 от 10.01.2024 признано прекращённым 20.02.2024 в связи с неисполнением». Что здесь требует маскирования: номер сделки, сам факт прекращения, обе части?</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>— (нет соответствующей сущности в текущем наборе, нужен отдельный документ)</t>
         </is>
       </c>
     </row>
@@ -1157,14 +1305,24 @@
           <t>Не маскируется</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Финансово-операционные данные, не именованная сущность</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>Пример: «Исходящий остаток по счёту клиента: 500 акций Газпром, плановый остаток на конец периода — 480 акций». Считаются ли такие цифры конфиденциальными сами по себе (без ФИО в той же фразе), и если да — нужен отдельный тип?</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>— (нет соответствующей сущности в текущем наборе, нужен отдельный документ)</t>
         </is>
       </c>
     </row>
@@ -1194,14 +1352,24 @@
           <t>Не маскируется</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Документ целиком; вложенные ФИО/суммы распознаются отдельно, но не как категория</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>Пример: «Поручение клиента Кузнецова К.К. на покупку 200 облигаций ОФЗ-26238 на сумму 210 000 руб.». Маскировать ли поручение как документ целиком, или только вложенные ФИО/суммы (уже покрыты существующими типами)?</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>— (в наборе нет документа-поручения; ближайший по смыслу — 03-reestr-operaciy, но это не поручение)</t>
         </is>
       </c>
     </row>
@@ -1231,14 +1399,24 @@
           <t>Не маскируется</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Аналогично п. 1.4</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>Пример: «Поручение на продажу 10 000 USD по курсу 92,50». Аналогично п. 1.4: маскировать текст поручения целиком или только сумму/курс как отдельную категорию?</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>— (нет соответствующей сущности в текущем наборе, нужен отдельный документ)</t>
         </is>
       </c>
     </row>
@@ -1263,19 +1441,29 @@
           <t>ORG (частично)</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Частично</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Название юрлица распознаётся, но сама информация о взаимоотношениях — нет</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>— (в наборе нет документа с юрлицами-контрагентами)</t>
         </is>
       </c>
     </row>
@@ -1305,14 +1493,24 @@
           <t>Не маскируется</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>Договорная информация, не PII-сущность</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>Пример: «По агентскому соглашению с ООО «Брокер-Партнёр» комиссия составляет 0,15% от объёма сделок клиентов, привлечённых партнёром». Считаются ли условия соглашения (ставка, объём) данными для маскирования, или это регулируется NDA/договором вне PII-маскировщика?</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>— (нет соответствующей сущности в текущем наборе, нужен отдельный документ)</t>
         </is>
       </c>
     </row>
@@ -1342,14 +1540,24 @@
           <t>Не маскируется</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>IT-инфраструктура, вне скоупа PII-маскировщика</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>Пример: «Доступ к модулю «Клиентские счета» имеют роли: Операционист, Старший операционист, Руководитель отдела». Подтвердите: этот пункт закрывается организационными/техническими мерами (RBAC, журналирование доступа), а не PII-маскировщиком?</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>— (не PII-документ, вне охвата test-tracker)</t>
         </is>
       </c>
     </row>
@@ -1379,14 +1587,24 @@
           <t>Не маскируется</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>IT-инфраструктура, вне скоупа PII-маскировщика</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>Пример: «Сотруднику Смирнову А.А. предоставлен доступ уровня «Администратор» к CRM». ФИО сотрудника уже маскируется — нужно ли отдельно маскировать сам факт/уровень предоставленных прав доступа?</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>— (не PII-документ, вне охвата test-tracker)</t>
         </is>
       </c>
     </row>
@@ -1416,14 +1634,24 @@
           <t>Не маскируется</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>IT-инфраструктура, вне скоупа PII-маскировщика</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>Пример: «Схема сети: DMZ 10.10.1.0/24 → firewall → внутренний сегмент 10.10.2.0/24, сервер itq-db-01». Нужен ли отдельный тип для IP-адресов/имён серверов (сейчас не входит во встроенные типы)?</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>— (не PII-документ, вне охвата test-tracker)</t>
         </is>
       </c>
     </row>
@@ -1453,14 +1681,24 @@
           <t>Не маскируется</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>Исходный код, вне скоупа PII-маскировщика</t>
         </is>
       </c>
-      <c r="G26" s="7" t="inlineStr">
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>Пример: фрагмент внутреннего скрипта расчёта комиссии, вставленный в чат с ИИ. Требуется построчное маскирование кода, или предполагается полный запрет на передачу кода в ИИ (политика уровня п. 5.1) без частичного маскирования?</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>— (не PII-документ, вне охвата test-tracker)</t>
         </is>
       </c>
     </row>
@@ -1490,14 +1728,24 @@
           <t>Не маскируется</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>Организационно-техническая ИБ-информация</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>Пример: «Используется двухфакторная аутентификация и шифрование AES-256 для хранения данных клиентов». Считать ли названия методов/технологий защиты данными для маскирования, или контроль обеспечивается запретом передачи таких документов в ИИ?</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>— (не PII-документ, вне охвата test-tracker)</t>
         </is>
       </c>
     </row>
@@ -1527,14 +1775,24 @@
           <t>Не маскируется</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>Организационно-техническая ИБ-информация</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>Пример: «Сотрудники проходят проверку службой безопасности и подписывают NDA сроком на 3 года». Маскировать ли описание процедур, или только ФИО упомянутых сотрудников (уже покрывается)?</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>— (не PII-документ, вне охвата test-tracker)</t>
         </is>
       </c>
     </row>
@@ -1564,14 +1822,24 @@
           <t>Не маскируется</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>Организационно-техническая ИБ-информация</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>Пример: «Резервный дата-центр расположен по адресу [адрес], время переключения — 15 минут». Маскировать ли адрес объекта (тип ADDRESS настроен на адреса физлиц, не гарантированно сработает на адрес ЦОД) и технические параметры?</t>
+        </is>
+      </c>
+      <c r="I29" s="8" t="inlineStr">
+        <is>
+          <t>— (не PII-документ, вне охвата test-tracker)</t>
         </is>
       </c>
     </row>
@@ -1601,14 +1869,24 @@
           <t>Не маскируется</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Организационно-техническая ИБ-информация</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>Пример: «Установлена система видеонаблюдения Hikvision DS-2CD2, СКУД Perco». Нужно ли маскировать названия/модели используемых средств защиты как отдельную категорию?</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>— (не PII-документ, вне охвата test-tracker)</t>
         </is>
       </c>
     </row>
@@ -1638,14 +1916,24 @@
           <t>Не маскируется</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>Организационно-техническая ИБ-информация</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>Пример: «Пропускной режим: турникеты на 1 этаже, пост охраны круглосуточно, видеонаблюдение периметра». Считается ли такое описание конфиденциальным для маскирования в документах, обрабатываемых ИИ?</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>— (не PII-документ, вне охвата test-tracker)</t>
         </is>
       </c>
     </row>
@@ -1675,14 +1963,24 @@
           <t>Не маскируется</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Организационно-техническая ИБ-информация</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>Пример: «По итогам пентеста в марте 2024 выявлено 3 уязвимости критического уровня в модуле авторизации». Маскировать ли содержание отчёта (находки, уязвимости) как отдельную категорию, или предполагается полный запрет на загрузку таких отчётов в систему?</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>— (не PII-документ, вне охвата test-tracker)</t>
         </is>
       </c>
     </row>
@@ -1712,14 +2010,24 @@
           <t>Не маскируется</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>Зонтичная политика («не отправлять в ИИ сведения из разделов 1–4»), не отдельный тип данных</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>Пример: сотрудник загружает в чат с ИИ выписку по счёту клиента для анализа. Как должна работать проверка: блокировка загрузки документа целиком при обнаружении данных из разделов 1–4, или маскирование конкретных полей перед отправкой в модель?</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>— (политика уровня загрузки, не конкретный документ; для прогона см. любой файл из test-tracker.xlsx)</t>
         </is>
       </c>
     </row>
@@ -1749,21 +2057,31 @@
           <t>Не маскируется</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>Зонтичная политика, не отдельный тип данных</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>Пример: ИИ в ответе процитировал фрагмент загруженного договора с ФИО и суммой. Должен ли ответ агента дополнительно проверяться/маскироваться перед показом пользователю, аналогично входящим документам?</t>
+        </is>
+      </c>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>— (политика уровня ответа агента, не конкретный документ)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1784,83 +2102,83 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>СВОДКА ПО СТАТУСАМ</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>Количество пунктов</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>Доля</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Маскируется</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n">
+      <c r="B4" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="17">
         <f>B4/30</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>Частично</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n">
+      <c r="B5" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="17">
         <f>B5/30</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>Не маскируется</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="n">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>Не маскируется</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="n">
         <v>22</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="17">
         <f>B6/30</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>Итого пунктов</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="20" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>Пункты «Не маскируется» — это преимущественно разделы 2–5 Перечня (контрагенты, IT-инфраструктура, ИБ-меры, политика работы с ИИ) и часть раздела 1 (номера договоров, финансово-операционные детали) — они не являются именованными PII-сущностями и требуют либо кастомных типов, либо контроля на уровне разграничения доступа/DLP, а не PII-маскирования. По каждому такому пункту в столбце «Вопрос к заказчику» на листе «Покрытие маскирования» сформулирован уточняющий вопрос с примером — ответы заказчика нужны, чтобы решить, где достаточно организационных/DLP-мер, а где требуется разработка кастомного PIIType.</t>
         </is>

--- a/docs/analysis/pokrytie-maskirovaniya-perechen-d8.xlsx
+++ b/docs/analysis/pokrytie-maskirovaniya-perechen-d8.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -105,8 +105,30 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="0093630F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00A8393B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00777777"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00A8393B"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -169,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -225,7 +247,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -788,9 +826,9 @@
           <t>Частично</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>Нет</t>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Да</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -798,9 +836,9 @@
           <t>Встроен только паспорт РФ; иные виды документов — нет</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>Пример: загранпаспорт, водительское удостоверение, вид на жительство иностранного клиента. Кроме паспорта РФ, какие ещё виды документов, удостоверяющих личность, реально встречаются в документах Общества и требуют отдельного типа?</t>
         </is>
       </c>
       <c r="I7" s="11" t="inlineStr">
@@ -963,7 +1001,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Информация о представителях, выгодоприобретателях и бенефициарных владельцах, любая иная информация в рамках идентификации</t>
+          <t>Информация о представителях, выгодоприобретателях и бенефициарных владельцах клиента, а также любая иная информация, предоставленная клиентом в рамках прохождения процедуры идентификации в Обществе</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -976,24 +1014,24 @@
           <t>Частично</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>Нет</t>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Да</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>ФИО таких лиц распознаётся, но сама роль/связь («выгодоприобретатель», «бенефициар») — не отдельная сущность</t>
-        </is>
-      </c>
-      <c r="H11" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t>— (роль/связь как отдельная сущность в наборе не смоделирована; ФИО — см. п. 1.2 выше)</t>
+          <t>ФИО таких лиц распознаётся, но сама роль/связь («выгодоприобретатель», «бенефициар») — не отдельная сущность; «любая иная информация» в рамках идентификации клиента (KYC) — открытый по формулировке пункт, потенциально широкий</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Пример: анкета клиента указывает «бенефициарный владелец — Иванов И.И., доля 40%». ФИО уже маскируется — нужно ли отдельно маскировать саму роль/связь («бенефициар», «представитель», доля владения)? И что конкретно имеется в виду под «любой иной информацией» в рамках идентификации — весь состав анкеты KYC?</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="inlineStr">
+        <is>
+          <t>01-anketa-klienta (частично — только ФИО клиента; роль/связь, доля владения, «иная информация» KYC в наборе не смоделированы)</t>
         </is>
       </c>
     </row>
@@ -1023,9 +1061,9 @@
           <t>Частично</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>Нет</t>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Да</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1033,9 +1071,9 @@
           <t>ФИО/наименование — да; внутренний уникальный код клиента — нет типа</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>Пример: «Клиент: Смирнов П.А., код клиента CL-000482». Внутренний код клиента не является общеупотребимым PII-форматом (не ИНН/СНИЛС) — нужен ли для него кастомный тип, и по какому шаблону формируются такие коды в системах Общества?</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr">
@@ -1077,12 +1115,12 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Известный пробел: «Номер договора» не входит во встроенные типы, нужен кастомный тип</t>
+          <t>Известный пробел: «Номер договора» не входит во встроенные типы. ВАЖНО: этот тип уже используется как целевая сущность в критерии приёмки пилота (manifest.json, docs/analysis/case-03-*) — риск, что приёмочный тест ≥98% натолкнётся на этот пробел раньше, чем придёт ответ заказчика.</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>Пример: «Договор № ИС-2024/0817 от 12.03.2024». Нужен ли отдельный кастомный тип «НОМЕР_ДОГОВОРА» для номера и даты, или достаточно маскирования ФИО/сумм, упомянутых рядом в тексте?</t>
+          <t>Наша рекомендация: завести кастомный тип «НОМЕР_ДОГОВОРА» по формату заказчика (пример: «Договор № ИС-2024/0817 от 12.03.2024»). Оговорка: у типа не будет контрольной суммы для валидации (она реализована только для ИНН/СНИЛС/карты/ОГРН/IBAN/VIN) — при разнородных форматах номеров у разных подразделений возможны ложные срабатывания/пропуски. Просим подтвердить формат(ы) номера договора и то, что дату рядом с номером тоже нужно маскировать.</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
@@ -1433,7 +1471,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Информация о внутренних и зарубежных контрагентах, партнёрах</t>
+          <t>Информация о внутренних и зарубежных контрагентах, партнёрах Общества, включая всю информацию, передаваемую данными лицами в рамках прохождения процедуры идентификации в Обществе</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -1446,19 +1484,19 @@
           <t>Частично</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
-        <is>
-          <t>Нет</t>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Да</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Название юрлица распознаётся, но сама информация о взаимоотношениях — нет</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Название юрлица распознаётся типом ORG; сама информация о взаимоотношениях — нет. У пункта есть вторая половина, аналогичная KYC по клиентам (п. 1.2): «вся информация, передаваемая... в рамках идентификации» — если контрагент физлицо/ИП или указывает контактных лиц, там применимы PERSON/PHONE/EMAIL/ADDRESS, как у клиентов</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>Пример: «Контрагент ООО «Брокер-Партнёр», контактное лицо — Сидоров А.П., тел. +7 999 000-00-00». Название юрлица и контактные ФИО/телефон уже маскируются существующими типами — нужно ли маскировать что-то ещё из «информации о взаимоотношениях» (условия, объёмы, роль контрагента)?</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
@@ -1500,7 +1538,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Договорная информация, не PII-сущность</t>
+          <t>Договорная информация, не PII-сущность Существующий кандидат для закрытия: собственный DLP-подобный механизм платформы (классификация текста + база защищаемых сведений + матрица получателей + блокировка/эскалация, работает автономно, без PIIType) — см. docs/rfi-responses/source/rfi-response-platform-ai-guard-extracted.md, §5.3. Вопрос заказчику стоит переформулировать: можно ли загрузить формулировку этого пункта Перечня в «базу защищаемых сведений» этого механизма.</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
@@ -1547,7 +1585,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>IT-инфраструктура, вне скоупа PII-маскировщика</t>
+          <t>IT-инфраструктура, вне скоупа PII-маскировщика Существующий кандидат для закрытия: собственный DLP-подобный механизм платформы (классификация текста + база защищаемых сведений + матрица получателей + блокировка/эскалация, работает автономно, без PIIType) — см. docs/rfi-responses/source/rfi-response-platform-ai-guard-extracted.md, §5.3. Вопрос заказчику стоит переформулировать: можно ли загрузить формулировку этого пункта Перечня в «базу защищаемых сведений» этого механизма.</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
@@ -1594,7 +1632,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>IT-инфраструктура, вне скоупа PII-маскировщика</t>
+          <t>IT-инфраструктура, вне скоупа PII-маскировщика Существующий кандидат для закрытия: собственный DLP-подобный механизм платформы (классификация текста + база защищаемых сведений + матрица получателей + блокировка/эскалация, работает автономно, без PIIType) — см. docs/rfi-responses/source/rfi-response-platform-ai-guard-extracted.md, §5.3. Вопрос заказчику стоит переформулировать: можно ли загрузить формулировку этого пункта Перечня в «базу защищаемых сведений» этого механизма.</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
@@ -1626,12 +1664,12 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>Не маскируется</t>
+          <t>IP (частично)</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>Частично</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -1641,17 +1679,17 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>IT-инфраструктура, вне скоупа PII-маскировщика</t>
+          <t>ИСПРАВЛЕНО при ревью: IP-адреса УЖЕ покрываются встроенным типом IP (см. docs/analysis/case-03-instrukciya-proverka-maskirovaniya.md, справочник 20 типов). Не покрыты: топология/схема сети как текст и произвольные имена серверов (не формат IP, отдельного типа нет)</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>Пример: «Схема сети: DMZ 10.10.1.0/24 → firewall → внутренний сегмент 10.10.2.0/24, сервер itq-db-01». Нужен ли отдельный тип для IP-адресов/имён серверов (сейчас не входит во встроенные типы)?</t>
+          <t>Пример: «Схема сети: DMZ 10.10.1.0/24 → firewall → внутренний сегмент 10.10.2.0/24, сервер itq-db-01». IP-адреса (10.10.1.0/24) уже маскируются типом IP — нужен ли отдельный тип для имён серверов (itq-db-01) и текстового описания топологии, или для этого пункта достаточно организационных мер (не выгружать схемы сети в ИИ вообще)?</t>
         </is>
       </c>
       <c r="I25" s="8" t="inlineStr">
         <is>
-          <t>— (не PII-документ, вне охвата test-tracker)</t>
+          <t>— (нет соответствующей сущности в текущем наборе; IP-тип не покрыт тестовыми документами anonymizer-2, нужен отдельный документ с IP-адресами)</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1706,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Программный код, разработанный Обществом или для Общества</t>
+          <t>Программный код, разработанный Обществом или для Общества в рамках договорных отношений с контрагентами</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -1688,12 +1726,12 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Исходный код, вне скоупа PII-маскировщика</t>
+          <t>Архитектурное ограничение (не просто пробел): NER-детектор платформы покрывает именованные сущности (PERSON/ORG/адреса/номера и т.п.), а не произвольный текст программного кода — построчное маскирование кода архитектурно не поддерживается Существующий кандидат для закрытия: собственный DLP-подобный механизм платформы (классификация текста + база защищаемых сведений + матрица получателей + блокировка/эскалация, работает автономно, без PIIType) — см. docs/rfi-responses/source/rfi-response-platform-ai-guard-extracted.md, §5.3. Вопрос заказчику стоит переформулировать: можно ли загрузить формулировку этого пункта Перечня в «базу защищаемых сведений» этого механизма.</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>Пример: фрагмент внутреннего скрипта расчёта комиссии, вставленный в чат с ИИ. Требуется построчное маскирование кода, или предполагается полный запрет на передачу кода в ИИ (политика уровня п. 5.1) без частичного маскирования?</t>
+          <t>Пример: фрагмент внутреннего скрипта расчёта комиссии, вставленный в чат с ИИ. Построчное маскирование кода платформа не умеет технически — предлагаем закрывать этот пункт полным запретом передачи файлов с кодом в ИИ (политика уровня п. 5.1/DLP, а не PII-маскирование). Подтверждаете такой подход?</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
@@ -1735,7 +1773,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Организационно-техническая ИБ-информация</t>
+          <t>Организационно-техническая ИБ-информация Существующий кандидат для закрытия: собственный DLP-подобный механизм платформы (классификация текста + база защищаемых сведений + матрица получателей + блокировка/эскалация, работает автономно, без PIIType) — см. docs/rfi-responses/source/rfi-response-platform-ai-guard-extracted.md, §5.3. Вопрос заказчику стоит переформулировать: можно ли загрузить формулировку этого пункта Перечня в «базу защищаемых сведений» этого механизма.</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
@@ -1782,7 +1820,7 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Организационно-техническая ИБ-информация</t>
+          <t>Организационно-техническая ИБ-информация Существующий кандидат для закрытия: собственный DLP-подобный механизм платформы (классификация текста + база защищаемых сведений + матрица получателей + блокировка/эскалация, работает автономно, без PIIType) — см. docs/rfi-responses/source/rfi-response-platform-ai-guard-extracted.md, §5.3. Вопрос заказчику стоит переформулировать: можно ли загрузить формулировку этого пункта Перечня в «базу защищаемых сведений» этого механизма.</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
@@ -1829,7 +1867,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Организационно-техническая ИБ-информация</t>
+          <t>Организационно-техническая ИБ-информация Существующий кандидат для закрытия: собственный DLP-подобный механизм платформы (классификация текста + база защищаемых сведений + матрица получателей + блокировка/эскалация, работает автономно, без PIIType) — см. docs/rfi-responses/source/rfi-response-platform-ai-guard-extracted.md, §5.3. Вопрос заказчику стоит переформулировать: можно ли загрузить формулировку этого пункта Перечня в «базу защищаемых сведений» этого механизма.</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
@@ -1876,7 +1914,7 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Организационно-техническая ИБ-информация</t>
+          <t>Организационно-техническая ИБ-информация Существующий кандидат для закрытия: собственный DLP-подобный механизм платформы (классификация текста + база защищаемых сведений + матрица получателей + блокировка/эскалация, работает автономно, без PIIType) — см. docs/rfi-responses/source/rfi-response-platform-ai-guard-extracted.md, §5.3. Вопрос заказчику стоит переформулировать: можно ли загрузить формулировку этого пункта Перечня в «базу защищаемых сведений» этого механизма.</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
@@ -1923,7 +1961,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Организационно-техническая ИБ-информация</t>
+          <t>Организационно-техническая ИБ-информация Существующий кандидат для закрытия: собственный DLP-подобный механизм платформы (классификация текста + база защищаемых сведений + матрица получателей + блокировка/эскалация, работает автономно, без PIIType) — см. docs/rfi-responses/source/rfi-response-platform-ai-guard-extracted.md, §5.3. Вопрос заказчику стоит переформулировать: можно ли загрузить формулировку этого пункта Перечня в «базу защищаемых сведений» этого механизма.</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
@@ -1970,7 +2008,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Организационно-техническая ИБ-информация</t>
+          <t>Организационно-техническая ИБ-информация Существующий кандидат для закрытия: собственный DLP-подобный механизм платформы (классификация текста + база защищаемых сведений + матрица получателей + блокировка/эскалация, работает автономно, без PIIType) — см. docs/rfi-responses/source/rfi-response-platform-ai-guard-extracted.md, §5.3. Вопрос заказчику стоит переформулировать: можно ли загрузить формулировку этого пункта Перечня в «базу защищаемых сведений» этого механизма.</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
@@ -2017,7 +2055,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Зонтичная политика («не отправлять в ИИ сведения из разделов 1–4»), не отдельный тип данных</t>
+          <t>Зонтичная политика («не отправлять в ИИ сведения из разделов 1–4»), не отдельный тип данных Существующий кандидат для закрытия: собственный DLP-подобный механизм платформы (классификация текста + база защищаемых сведений + матрица получателей + блокировка/эскалация, работает автономно, без PIIType) — см. docs/rfi-responses/source/rfi-response-platform-ai-guard-extracted.md, §5.3. Вопрос заказчику стоит переформулировать: можно ли загрузить формулировку этого пункта Перечня в «базу защищаемых сведений» этого механизма.</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
@@ -2064,7 +2102,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Зонтичная политика, не отдельный тип данных</t>
+          <t>Зонтичная политика, не отдельный тип данных Существующий кандидат для закрытия: собственный DLP-подобный механизм платформы (классификация текста + база защищаемых сведений + матрица получателей + блокировка/эскалация, работает автономно, без PIIType) — см. docs/rfi-responses/source/rfi-response-platform-ai-guard-extracted.md, §5.3. Вопрос заказчику стоит переформулировать: можно ли загрузить формулировку этого пункта Перечня в «базу защищаемых сведений» этого механизма.</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
@@ -2093,7 +2131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2136,7 +2174,7 @@
       </c>
       <c r="C4" s="17">
         <f>B4/30</f>
-        <v/>
+        <v>0.13333333333333333</v>
       </c>
     </row>
     <row r="5">
@@ -2146,11 +2184,11 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="17">
         <f>B5/30</f>
-        <v/>
+        <v>0.16666666666666666</v>
       </c>
     </row>
     <row r="6">
@@ -2160,11 +2198,11 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" s="17">
         <f>B6/30</f>
-        <v/>
+        <v>0.7</v>
       </c>
     </row>
     <row r="7">
@@ -2177,17 +2215,78 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
+    <row r="9">
       <c r="A9" s="21" t="inlineStr">
         <is>
-          <t>Пункты «Не маскируется» — это преимущественно разделы 2–5 Перечня (контрагенты, IT-инфраструктура, ИБ-меры, политика работы с ИИ) и часть раздела 1 (номера договоров, финансово-операционные детали) — они не являются именованными PII-сущностями и требуют либо кастомных типов, либо контроля на уровне разграничения доступа/DLP, а не PII-маскирования. По каждому такому пункту в столбце «Вопрос к заказчику» на листе «Покрытие маскирования» сформулирован уточняющий вопрос с примером — ответы заказчика нужны, чтобы решить, где достаточно организационных/DLP-мер, а где требуется разработка кастомного PIIType.</t>
+          <t>ИЗ НИХ «НЕ МАСКИРУЕТСЯ» — ПО ПРИЧИНЕ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Категория</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Кол-во пунктов</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>Доля от 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>Потенциальный кастомный PIIType (финансово-операционные детали, п. 1.3–1.5)</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="24">
+        <f>B12/30</f>
+        <v>0.26666666666666666</v>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>Структурно вне PII-маскировщика (IT/ИБ/AI-policy/оргданные — нужны RBAC/DLP, не новый тип)</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="n">
+        <v>13</v>
+      </c>
+      <c r="C13" s="24">
+        <f>B13/30</f>
+        <v>0.43333333333333335</v>
+      </c>
+    </row>
+    <row r="16" ht="92" customHeight="1">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>Пункты «Не маскируется» делятся на две разные по природе группы (см. таблицу выше): 8 пунктов раздела 1 (номера/даты договоров, сделки по счетам, займы, задолженность, прекращённые обязательства, остатки, поручения) — это финансово-операционные детали, для которых реалистично предложить кастомный PIIType; 13 пунктов (контрагентские соглашения, IT-инфраструктура, ИБ-меры, программный код, политика работы с ИИ) — структурно другой слой контроля, не PII-сущности. Для второй группы у платформы уже есть встроенный кандидат: собственный DLP-подобный механизм (классификация текста + база защищаемых сведений + матрица получателей + блокировка/эскалация, автономный, без PIIType) — см. docs/rfi-responses/source/rfi-response-platform-ai-guard-extracted.md, §5.3. По каждому пункту в столбце «Вопрос к заказчику» на листе «Покрытие маскирования» сформулирован уточняющий вопрос с примером и, где применимо, наша техническая рекомендация — не только открытый вопрос.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t>⚠ Риск для приёмки пилота: пункт 1.3 «Номера и даты договоров» (кастомный тип «НОМЕР_ДОГОВОРА» пока не реализован) уже используется как целевая сущность в manifest.json / критерии приёмки ≥98% (docs/analysis/case-03-pilot-tz-ai-guard.md) — до ответа заказчика на вопрос по этому пункту приёмочный тест может формально не набрать нужный процент именно из-за этого пробела.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A18:C18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/analysis/pokrytie-maskirovaniya-perechen-d8.xlsx
+++ b/docs/analysis/pokrytie-maskirovaniya-perechen-d8.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Покрытие маскирования" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Три слоя маскирования" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -131,8 +132,32 @@
       <color rgb="00A8393B"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000E6E63"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001E7A4C"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0093630F"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -164,6 +189,11 @@
         <fgColor rgb="00FBF0DC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000E6E63"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -191,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -266,6 +296,12 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2290,4 +2326,1405 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Три слоя детектирования и схема маскирования — по пунктам Перечня Д8 + общесистемные типы платформы</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="150" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Разбивка по механизму обнаружения, которым реально располагает платформа (docs/rfi-responses/, §2.3: «обнаружение ПДн тремя механизмами — аннотации каталога метаданных, свыше 250 формальных правил для типизированных идентификаторов (для шести типов — ИНН, СНИЛС, банковская карта, ОГРН, IBAN, VIN — дополнительно проверяются контрольные соотношения; для остальных — только распознавание по формату), NER для свободного текста (только ФИО/организации/география)»; плюс собственный DLP-механизм §5.3 для контента вне PII — классификация текста + база защищаемых сведений + матрица получателей + блокировка/эскалация, механизм работает автономно). Слой 1 — распознавание по формату (regex/шаблон), без вычисляемой контрольной суммы. Слой 2 — вычисляемые значения: контрольная сумма поверх самого значения, ТОЛЬКО шесть типов из RFI. Слой 3 — нет фиксированного формата вообще (организационный/описательный текст) — детектируется не значением, а смыслом формулировки через DLP-механизм платформы, а не PIIType. Один пункт Перечня может содержать поля из разных слоёв одновременно — тогда пункт присутствует в нескольких таблицах ниже. ВАЖНО: только фактическая принадлежность к списку из RFI помечена как подтверждённый факт; всё остальное (предложенные кастомные типы, гипотезы про механизм DLP, иллюстративные формулировки) — рабочие предложения инженера, требующие подтверждения вендором/заказчиком, помечены явно. Черновик подготовлен инженером, прошёл ревью тремя ролями (аналитик/архитектор/критик), правки внесены — см. столбец «Комментарий ревью» в каждой таблице.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>СЛОЙ 1 — Распознавание по формату (regex/шаблон, БЕЗ вычисляемой контрольной суммы)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>Пункт Перечня</t>
+        </is>
+      </c>
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>Что маскируем</t>
+        </is>
+      </c>
+      <c r="C5" s="29" t="inlineStr">
+        <is>
+          <t>Regex-шаблон (пример)</t>
+        </is>
+      </c>
+      <c r="D5" s="29" t="inlineStr">
+        <is>
+          <t>Пример совпадения</t>
+        </is>
+      </c>
+      <c r="E5" s="29" t="inlineStr">
+        <is>
+          <t>Надёжность</t>
+        </is>
+      </c>
+      <c r="F5" s="29" t="inlineStr">
+        <is>
+          <t>Тип платформы / статус</t>
+        </is>
+      </c>
+      <c r="G5" s="29" t="inlineStr">
+        <is>
+          <t>Комментарий ревью</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>ФИО по ключу («ФИО:», «Ф.И.О.»)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>(?:ФИО|Ф\.?И\.?О\.?)\s*[:\-]?\s*[А-ЯЁ][а-яё]+\s[А-ЯЁ][а-яё]+(?:\s[А-ЯЁ][а-яё]+)?</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>ФИО: Смирнов Пётр Александрович</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Высокая</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>FULL_NAME — маскируется</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Regex ловит ключ-значение. Свободное упоминание ФИО без ключевого слова — отдельный механизм, NER, не regex (см. примечание под таблицей)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Фирменное наименование клиента-юрлица</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>(?:ООО|ПАО|АО|ЗАО|ИП)\s[«\"][^»\"]{2,60}[»\"]</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Брокер-Партнёр»</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Высокая</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>ORG — не выделено отдельным пунктом для клиента (есть для контрагента, п. 2.1)</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Добавлено при ревью (аналитик): в исходной таблице ORG-пример был только для контрагентов (2.1), не для клиента-юрлица из 1.3 — по факту тот же механизм (regex по организационно-правовой форме + NER на название)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Номер телефона</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>(?:\+7|8)[\s\-]?\(?\d{3}\)?[\s\-]?\d{3}[\s\-]?\d{2}[\s\-]?\d{2}</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>+7 916 123-45-67</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Высокая</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>PHONE — маскируется</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Адрес электронной почты</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>[A-Za-z0-9._%+\-]+@[A-Za-z0-9.\-]+\.[A-Za-z]{2,}</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>p.smirnov.test@example.ru</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Высокая</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>EMAIL — маскируется</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Адрес фактического места жительства / регистрации</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>г\.?\s?[А-ЯЁ][а-яё]+.{0,60}?(?:ул\.|улица|пр-т|проспект|д\.|дом).{0,30}</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>г. Москва, ул. Тестовая, д. 12, кв. 5</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>Средняя</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>ADDRESS — маскируется</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Формат-эвристика, не строгий regex: структура адреса вариативна, реальный детектор ближе к NER+словарь географических названий, чем к одному шаблону</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Паспорт РФ — серия и номер</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>\d{2}\s?\d{2}\s?\d{6}</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>4510 123456</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>Средняя</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>PASSPORT — частично (только паспорт РФ)</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Контрольной суммы у номера паспорта РФ нет — это слой 1, не слой 2. Найдено при ревью (архитектор): без привязки к ключевому слову рядом («паспорт», «серия») любые 10 цифр подряд (кусок счёта/телефона) дадут ложное срабатывание — на практике нужен контекстный якорь, как у даты рождения ниже</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Место выдачи паспорта</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>(?:выдан|код подразделения)\s*[:\-]?\s*.{5,80}</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>выдан ОВД района Хамовники г. Москвы</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Низкая</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>не выделено отдельным PIIType</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Ключ-значение эвристика, высокий риск ложных срабатываний без ключевого слова рядом</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>1.2 / 1.3</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Дата рождения (в связке с ключевым словом)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>(?:дата рождения|д\.р\.)\s*[:\-]?\s*\d{2}\.\d{2}\.\d{4}</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>дата рождения: 14.03.1985</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>Средняя</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>DOB — формальное правило платформы (RFI, §2.3), не выделено отдельным пунктом Перечня явно</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Без ключевого слова рядом — слишком много ложных срабатываний на любые даты в документе</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Банковский счёт (20 цифр)</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>\d{20}</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>40817810900001234567</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>Средняя</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>BANK_ACCOUNT — формальное правило платформы (RFI, §2.3)</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>ИСПРАВЛЕНО при ревью (аналитик+архитектор, независимо): изначально был в слое 2 со ссылкой на RFI как на контрольную сумму — ошибка. RFI прямо называет шестью checksum-типами ИНН/СНИЛС/карту/ОГРН/IBAN/VIN, банковский счёт — в списке «остальных, распознаваемых по формату». Реальный алгоритм ЦБ РФ для счёта существует (веса 7,1,3 по разрядам БИК+счёта), но RFI не подтверждает, что платформа его применяет — поэтому здесь, не в слое 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>IP-адрес</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>\b(?:\d{1,3}\.){3}\d{1,3}(?:/\d{1,2})?\b</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>10.10.1.0/24</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Высокая</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>IP — маскируется (частично, см. п. 3.3)</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Подтверждено при ревью: тип IP уже встроен, ранее ошибочно значился как непокрытый</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Имя сервера / хостнейм (предлагается)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>[a-z0-9]([a-z0-9\-]{0,61}[a-z0-9])?\.(?:local|internal|corp)\b</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>itq-db-01.internal</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Низкая</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>не входит во встроенные типы — предложение</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>ЧЕРНОВИК — не подтверждено. Открытый вопрос заказчику: подтвердить домен внутренней сети, чтобы не ловить произвольные слова с точкой</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Номер договора (предлагается, кастомный тип)</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>№?\s?[А-ЯA-Z]{2,10}(?:[\-/][A-Za-zА-я0-9]+){1,5}</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>ИКД-1-PRO-TEST-001</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Низкая</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>не входит во встроенные типы — предложение</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>ЧЕРНОВИК — не подтверждено. ИСПРАВЛЕНО при ревью (архитектор): исходный regex содержал опечатку в символьном классе (латинская A вместо кириллической А создавала диапазон на 1000+ лишних символов) и физически не матчил собственный пример — переписан. Контрольной суммы нет; формат у разных подразделений заказчика не подтверждён</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Уникальный код клиента (предлагается)</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>CL[\-_]?\d{4,8}</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>CL-000482</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Низкая</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>не входит во встроенные типы — предложение</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>ЧЕРНОВИК — не подтверждено. Формат гипотетический, реальный шаблон кода клиента у заказчика не подтверждён</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>СЛОЙ 2 — Вычисляемые значения (контрольная сумма — ТОЛЬКО 6 типов, подтверждённых RFI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Ни один из этих типов не назван в Перечне Д8 буквально — RFI подтверждает контрольную сумму ровно для шести типов (ИНН, СНИЛС, банковская карта, ОГРН, IBAN, VIN), они добавлены здесь для полноты технической картины и как контекст: часть из них используется в тестовых данных пилота, часть релевантна отдельным пунктам Перечня по смыслу (см. столбец «Связь с Перечнем»). VIN (транспортные средства) в таблицу не включён — неприменим ни к одному пункту Перечня Д8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="29" t="inlineStr">
+        <is>
+          <t>Связь с Перечнем</t>
+        </is>
+      </c>
+      <c r="B22" s="29" t="inlineStr">
+        <is>
+          <t>Что маскируем</t>
+        </is>
+      </c>
+      <c r="C22" s="29" t="inlineStr">
+        <is>
+          <t>Алгоритм проверки</t>
+        </is>
+      </c>
+      <c r="D22" s="29" t="inlineStr">
+        <is>
+          <t>Пример</t>
+        </is>
+      </c>
+      <c r="E22" s="29" t="inlineStr">
+        <is>
+          <t>Тип платформы / статус</t>
+        </is>
+      </c>
+      <c r="F22" s="29" t="inlineStr">
+        <is>
+          <t>Комментарий ревью</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>не названо в Перечне буквально</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>ИНН физлица (12 цифр)</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Контрольная цифра 11: (7,2,4,10,3,5,9,4,6,8) · (d1…d10), сумма mod 11, затем mod 10. Контрольная цифра 12: (3,7,2,4,10,3,5,9,4,6,8) · (d1…d11), аналогично mod 11 mod 10</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>770912345616</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>INN — подтверждено RFI (§2.3, один из 6 checksum-типов)</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>ИСПРАВЛЕНО при ревью (архитектор): в черновике были неверные веса (11 чисел вместо правильных 10/11) и ложная атрибуция «ЦБ/ФНС» — алгоритм регулирует только ФНС, ЦБ здесь ни при чём. Веса выше выверены по официальному алгоритму ФНС</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>1.2 (по смыслу, «данные документов»)</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>СНИЛС</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Сумма (цифра × вес, вес 9→1 по первым 9 цифрам) по модулю 101; если сумма &lt; 100 — контрольное число равно самой сумме; если сумма = 100 или 101 — контрольное число «00»</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>123-456-789 64</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>SNILS — подтверждено RFI (§2.3)</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Не выделен отдельным пунктом Перечня — входит в «данные документов, удостоверяющих личность» по смыслу, требует подтверждения у заказчика</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>не в Перечне (общесистемный тип)</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Банковская карта</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Алгоритм Луна: справа налево удваивать каждую вторую цифру, если результат ≥10 — вычесть 9, сумма всех цифр должна делиться на 10 без остатка</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>4111 1111 1111 1111</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>BANK_CARD — подтверждено RFI (§2.3)</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>ИСПРАВЛЕНО при ревью (архитектор): пример из черновика («…1234») не проходит алгоритм Луна — заменён на стандартный тестовый номер, реально проходящий проверку</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>2.1 (если код контрагента = ОГРН)</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>ОГРН / ОГРНИП</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>ОГРН (13 цифр): 13-й разряд = (первые 12 цифр mod 11) mod 10. ОГРНИП (15 цифр): аналогично по модулю 13</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>1027700123450</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>OGRN — подтверждено RFI (§2.3)</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Релевантно, если «уникальный код» контрагента/юрлица в п. 2.1 фактически ОГРН — требует подтверждения у заказчика</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>1.5 (если расчёты через зарубежный счёт)</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>IBAN</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Контрольная сумма ISO 7064 (mod 97): переставить первые 4 символа в конец, буквы → цифры (A=10…Z=35), остаток от деления на 97 должен быть равен 1</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>DE89 3704 0044 0532 0130 00</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>IBAN — подтверждено RFI (§2.3)</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Релевантно для п. 1.5 «поручения на покупку/продажу иностранной валюты», если расчёты идут через зарубежный счёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>СЛОЙ 3 — Примеры формулировок для DLP (нет фиксированного значения, только смысл)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="76" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>⚠ Слой с наименьшей надёжностью из трёх. RFI (§5.3) подтверждает только сам факт наличия у платформы механизма «классификация текста + база защищаемых сведений» — конкретный метод (ключевые слова/фразы, как условно показано ниже, или более устойчивая семантическая модель) вендором не детализирован; формулировка «DLP по ключевым фразам» в таблице — рабочая ГИПОТЕЗА инженера, не факт из RFI. Ключевой практический риск: поиск по ключевым словам/фразам обходится перефразированием, синонимами, англицизмами (например «NDA» вместо «соглашение о неразглашении») и опечатками — то есть это в принципе менее надёжный слой, чем 1 и 2, и должен быть проверен на реальных документах Д8 в ходе пилота, а не воспринят как готовое покрытие. Все формулировки ниже, кроме п. 1.1 (пример самого заказчика), — иллюстративные примеры инженера, не выдержки из реальных документов Д8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="29" t="inlineStr">
+        <is>
+          <t>Пункт Перечня</t>
+        </is>
+      </c>
+      <c r="B31" s="29" t="inlineStr">
+        <is>
+          <t>Категория</t>
+        </is>
+      </c>
+      <c r="C31" s="29" t="inlineStr">
+        <is>
+          <t>Пример формулировки (что ищем)</t>
+        </is>
+      </c>
+      <c r="D31" s="29" t="inlineStr">
+        <is>
+          <t>Как предлагаем скрывать</t>
+        </is>
+      </c>
+      <c r="E31" s="29" t="inlineStr">
+        <is>
+          <t>Комментарий ревью</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Индивидуальные схемы обслуживания</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>«Обслуживание по индивидуальному тарифному плану с персональным менеджером», «особые условия обслуживания счёта клиента»</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>DLP-механизм платформы (§5.3): база защищаемых сведений + блокировка/эскалация</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Единственный пример, сформулированный самим заказчиком в исходном запросе (лист «Покрытие маскирования»)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Роль представителя/бенефициара (не само ФИО)</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>«выгодоприобретатель — …», «бенефициарный владелец — …, доля 40%»</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>DLP по ключевым словам «выгодоприобретатель», «бенефициар», «представитель» (гипотеза механизма — см. примечание ниже)</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>ФИО в этой же фразе покрывается отдельно (слой 1/NER), здесь — только роль/связь. Иллюстративный пример, не из реального документа Д8</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Содержание сделки (актив, объём — без суммы)</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>«совершена сделка на покупку 100 акций Сбербанк»</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>DLP по паттерну «сделка на покупку/продажу [актив]»; сумма сделки — отдельно слой 1 (денежный формат)</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Составной случай: сумма и номер счёта уже маскируются, содержание сделки как категория — нет. Иллюстративный пример</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Маржинальные займы (условия)</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>«предоставлен маржинальный заём в размере … под …% годовых»</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>DLP по ключевой фразе «маржинальный заём»; сумма — слой 1</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Иллюстративный пример, не из реального документа Д8</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Задолженность (факт)</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>«задолженность клиента составляет …», «просроченная задолженность по счёту»</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>DLP по ключевой фразе «задолженность»; сумма — слой 1</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Иллюстративный пример, не из реального документа Д8</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Прекращённые/неисполненные обязательства</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>«обязательство … признано прекращённым/не исполненным»</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>DLP по ключевым фразам «обязательство прекращено», «не исполнено»; номер сделки — слой 1 (regex)</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Иллюстративный пример, не из реального документа Д8</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Исходящий остаток по активу</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>«исходящий остаток по счёту: 500 акций Газпром, плановый остаток — 480 акций»</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>DLP по ключевой фразе «исходящий остаток»</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Открытый вопрос: считать ли остаток конфиденциальным без привязки к ФИО в той же фразе</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Поручение на сделку с финансовым инструментом (документ целиком)</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>«поручение клиента на покупку/продажу [инструмент] на сумму …»</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Блокировка документа целиком по классу «поручение», а не построчное маскирование</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Вложенные ФИО/суммы покрываются отдельно; сам факт/тип поручения — только через DLP-классификацию документа</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Поручение на валютную операцию (документ целиком)</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>«поручение на продажу 10 000 USD по курсу 92,50»</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Аналогично п. 1.4 — блокировка документа/DLP-классификация</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Иллюстративный пример, не из реального документа Д8</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Информация о взаимоотношениях с контрагентом</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>«по договору с контрагентом ООО «…» установлены следующие условия…»</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>DLP по ключевым фразам «условия договора», «взаимоотношения с контрагентом»; название юрлица — отдельно NER (ORG)</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Иллюстративный пример, не из реального документа Д8</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Условия партнёрских программ</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>«комиссия по агентскому соглашению составляет 0,15% от объёма сделок»</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>DLP по ключевым фразам «агентское соглашение», «партнёрская программа»</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Иллюстративный пример, не из реального документа Д8</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Система разграничения доступа (описание)</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>«доступ к модулю «Клиентские счета» имеют роли: Операционист, Старший операционист»</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Не PII вообще — предлагается закрывать оргмерами/RBAC, а не DLP-детектором текста</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Формально слой 3 по просьбе проработать пример для каждого пункта, но по сути это вне PII-маскировщика в принципе</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Права доступа сотрудников</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>«сотруднику … предоставлен доступ уровня «Администратор» к CRM»</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Аналогично п. 3.1 — оргмеры/RBAC, не DLP по тексту</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>ФИО сотрудника в этой же фразе покрывается отдельно</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Топология/схема сети (текстовое описание, не сами IP)</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>«схема сети: DMZ → firewall → внутренний сегмент, сервер …»</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>DLP по ключевым словам «схема сети», «DMZ», «сегмент сети»; IP-адреса и хостнеймы — отдельно слой 1</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Иллюстративный пример, не из реального документа Д8</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Программный код</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Синтаксические признаки кода (отступы, скобки, ключевые слова языка), не текстовая формулировка</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Не поддерживается ни один из трёх слоёв — предлагается блокировка по расширению/MIME-типу файла на входном шлюзе до индексации/отправки в ИИ</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Уточнено при ревью (архитектор): список поддерживаемых форматов платформы (PDF/DOCX/DOC/TXT/MD/CSV/XLSX/JSON/XML — RFI) не включает файлы кода, это технически упрощает блокировку на входе, а не через анализ содержимого</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Методы/способы защиты информации</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>«используется двухфакторная аутентификация и шифрование AES-256»</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>DLP по ключевым словам названий методов защиты</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Иллюстративный пример, не из реального документа Д8</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Меры безопасности персонала</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>«сотрудники проходят проверку службой безопасности, подписывают NDA»</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>DLP по ключевым фразам «проверка службой безопасности», «NDA»</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Иллюстративный пример, не из реального документа Д8</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Меры по критической инфраструктуре</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>«резервный дата-центр расположен по адресу …, время переключения 15 минут»</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Адрес объекта — слой 1 (эвристика ADDRESS/LOC); технические параметры (время переключения) — DLP по ключевым словам</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Иллюстративный пример, не из реального документа Д8</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Названия/модели средств защиты</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>«установлена система видеонаблюдения Hikvision DS-2CD2, СКУД Perco»</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>DLP по словарю моделей оборудования (список, не regex — названия непредсказуемо разнообразны)</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Иллюстративный пример, не из реального документа Д8</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Охрана / пропускной режим</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>«турникеты на 1 этаже, пост охраны круглосуточно»</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>DLP по ключевым словам «пропускной режим», «пост охраны»</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Иллюстративный пример, не из реального документа Д8</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Результаты проверок/аудитов/пентестов</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>«по итогам пентеста выявлено 3 уязвимости критического уровня»</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>DLP по ключевым словам «пентест», «аудит», «уязвимость»</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Иллюстративный пример, не из реального документа Д8</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="56" customHeight="1">
+      <c r="A54" s="26" t="inlineStr">
+        <is>
+          <t>П. 5.1 и 5.2 Перечня («материалы для ИИ» / «результаты ИИ», если содержат сведения из разделов 1–4) намеренно не включены в таблицу выше строкой: это не текстовая формулировка для поиска, а зонтичное правило агрегации результатов остальных слоёв («заблокировать документ/ответ, если сработал любой из слоёв 1–3 на контенте из разделов 1–4»). Перенесено сюда при ревью (критик): в таблице формулировок пустая ячейка «пример» читалась как пропуск данных, а не как осознанное исключение.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="70" customHeight="1">
+      <c r="A56" s="26" t="inlineStr">
+        <is>
+          <t>Примечание про ФИО и организации: свободное упоминание имени/организации в связном тексте (не по ключу «ФИО:») распознаётся не регулярным выражением, а NER-моделью (третий из трёх официальных механизмов детектирования платформы, см. RFI §2.3) — отдельный способ обнаружения, который не укладывается ровно ни в один из трёх запрошенных слоёв. В таблицах выше он условно отнесён к слою 1 там, где встречается по ключевому слову (regex-обвязка вокруг NER-результата); свободные упоминания ФИО/организаций в тексте документа технически ближе к слою 3 по механизму (не по формату значения, а по контексту).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A56:I56"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A54:I54"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/analysis/pokrytie-maskirovaniya-perechen-d8.xlsx
+++ b/docs/analysis/pokrytie-maskirovaniya-perechen-d8.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Покрытие маскирования" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Три слоя маскирования" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Частичное маскирование" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -156,6 +157,18 @@
       <color rgb="0093630F"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00A8393B"/>
+      <sz val="12"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -221,7 +234,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -302,6 +315,16 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3727,4 +3750,479 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Стратегия частичного маскирования: «скрываем ПДн + название компании, остальное — нет» — разбор на реальном документе</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="70" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Повод: реальный «Отчёт брокера» (форма брокерской отчётности РФ), загруженный заказчиком. Вопрос заказчика: если замаскировать документ целиком не удаётся (технически не всё покрыто типами, либо аналитике нужны реальные цифры), достаточно ли скрыть (а) персональные данные и (б) название компании-брокера, оставив остальное (номер договора, номера счетов, состав портфеля, остатки) как есть — не будет ли это концептуальной утечкой? Обсуждение проведено тем же составом трёх ролей (аналитик/архитектор/критик), что и на листе «Три слоя маскирования» — независимо друг от друга, затем сведено ниже.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="32" t="inlineStr">
+        <is>
+          <t>ДОКУМЕНТ-ПРИМЕР (расшифровано со скриншота заказчика)</t>
+        </is>
+      </c>
+      <c r="B4" s="33" t="n"/>
+      <c r="C4" s="33" t="n"/>
+      <c r="D4" s="33" t="n"/>
+      <c r="E4" s="33" t="n"/>
+      <c r="F4" s="33" t="n"/>
+    </row>
+    <row r="5" ht="62" customHeight="1">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>БРОКЕР: АО «Инвестиционная компания Д8», лицензия проф. участника РЦБ № 045-0751…, адрес: 123112, Москва, Пресненский р-н. ОТЧЁТ БРОКЕРА за период 26.06.2026–26.06.2026. Клиент: Ожигихин Юрий Юрьевич. Договор № ВР33431 от 24.09.2019; брокерский счёт ВР33431; лицевой счёт ВР33431-МО-01. Остатки ДС и баланс счёта: 16 634,88 → 16 623,07 руб. Портфель (начало/конец периода): ОФЗ-ПД225 (ISIN RU000A0ZYUB7) — 1,00 шт; ВТБ ПАО ао07 (RU000A0JP5V6) — 13,00 шт; Сбербанк ПАО ао03 (RU0009029540) — 6,00 шт; паи БПИФ «Т-Капитал Стратегия ВПв Рублях» (RU000A1011U5) — 1,00 шт; USD — 4,00. Подписи: Корчагин В.В. (уполномоченное лицо), Губарева С.А. (нач. отдела учёта и отчётности).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>ВЕРДИКТ</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="n"/>
+      <c r="C7" s="36" t="n"/>
+      <c r="D7" s="36" t="n"/>
+      <c r="E7" s="36" t="n"/>
+      <c r="F7" s="36" t="n"/>
+    </row>
+    <row r="8" ht="62" customHeight="1">
+      <c r="A8" s="37" t="inlineStr">
+        <is>
+          <t>ДА — предложенная стратегия («скрыть только ФИО + название компании») концептуально ЯВЛЯЕТСЯ утечкой. Единогласный вывод всех трёх ролей. Причина не в том, что маскирование PII работает плохо, а в том, что оно решает не ту задачу: большая часть чувствительного в этом документе — не персональные данные (регулируются 152-ФЗ), а профессиональная/коммерческая тайна брокера (регулируется ФЗ «О рынке ценных бумаг», ст. 3.1, и собственным Перечнем коммерческой тайны заказчика — см. лист «Покрытие маскирования»). «Не ПДн» ≠ «не тайна»: номер договора, номера счетов, состав портфеля и остатки прямо названы в Перечне заказчика (п. 1.3) и уже задокументированы там статусом «Не маскируется».</t>
+        </is>
+      </c>
+      <c r="B8" s="36" t="n"/>
+      <c r="C8" s="36" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="36" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>ЧТО ДЕМАСКИРУЕТ КЛИЕНТА/КОМПАНИЮ ВОПРЕКИ СТРАТЕГИИ</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="n"/>
+      <c r="C10" s="33" t="n"/>
+      <c r="D10" s="33" t="n"/>
+      <c r="E10" s="33" t="n"/>
+      <c r="F10" s="33" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>Что остаётся открытым</t>
+        </is>
+      </c>
+      <c r="B11" s="29" t="inlineStr">
+        <is>
+          <t>Серьёзность</t>
+        </is>
+      </c>
+      <c r="C11" s="29" t="inlineStr">
+        <is>
+          <t>Почему это проблема</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="inlineStr">
+        <is>
+          <t>Какая роль нашла</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Номер договора / счёта (ВР33431, ВР33431-МО-01)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Критично</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Уже задокументированный пробел (лист «Покрытие маскирования», п. 1.3 «Номера и даты договоров» — «Не маскируется»). Работает как стабильный join-ключ: стоит ему один раз всплыть в связке с ФИО в любом другом источнике — оба факта корректно склеиваются задним числом, даже если в ЭТОМ документе ФИО замаскировано</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Аналитик + Архитектор + Критик (независимо)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Номер лицензии брокера (045-0751…) и юр. адрес</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Критично</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Публично ищется в реестре ЦБ РФ за секунды — однозначно указывает на конкретную компанию независимо от того, замаскирована ли строка с названием. Маскировать только название компании, оставляя лицензию открытой, — не даёт защиты</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Аналитик + Архитектор</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Точный состав портфеля + остатки на конкретную дату</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Критично</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>5 конкретных бумаг с точными количествами (1 / 13 / 6 / 1 / 4) + баланс до копейки на конкретный день — уникальный «отпечаток» портфеля. Квазиидентификатор: набор атрибутов сам по себе резко сужает круг возможных владельцев (принцип k-anonymity) — деанонимизация возможна без прямого доступа к ФИО, при пересечении с любым другим источником</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Аналитик + Архитектор + Критик</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>ФИО сотрудников-подписантов (Корчагин В.В., Губарева С.А.)</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Важно</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Если правило маскирования настроено «прятать поле „Клиент:“», а не «прятать любую PERSON-сущность», подписи сотрудников останутся открытыми — реалистичный риск конфигурации, не проверен на этом документе</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Критик</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Само поле «Клиент: Ожигихин Юрий Юрьевич»</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Уточнить</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Существующий regex слоя 1 заточен под ключ «ФИО:»/«Ф.И.О.», а в отчёте ключ — «Клиент:». Сработает только NER (без гарантии), либо нужно расширить шаблон отдельным ключевым словом «Клиент:»</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Архитектор</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Структурные артефакты формы (разделы 1–8.2, площадка ФОРТС, текст дисклеймеров, НКО-депозитарий)</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Уточнить</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Если это единый регуляторный шаблон ЦБ РФ, используемый многими брокерами, — не проблема (форма не уникальна для Д8). Если форма/вёрстка специфична для ПО, которым пользуется именно Д8, — узнаваемый отпечаток компании в обход замаскированного названия. Требует уточнения у заказчика, не выяснено эмпирически</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Аналитик + Критик (разошлись в оценке, честно помечено как открытый вопрос)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>ISIN ценных бумаг сам по себе</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Не проблема</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Публичный биржевой идентификатор, не привязан к конкретному брокеру/клиенту. Демаскирование ISIN само по себе не создаёт риска — проблема только в сочетании ISIN + количество + счёт + дата (агрегация)</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Архитектор</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="32" t="inlineStr">
+        <is>
+          <t>КЛЮЧЕВЫЕ ТЕЗИСЫ ПО РОЛЯМ</t>
+        </is>
+      </c>
+      <c r="B20" s="33" t="n"/>
+      <c r="C20" s="33" t="n"/>
+      <c r="D20" s="33" t="n"/>
+      <c r="E20" s="33" t="n"/>
+      <c r="F20" s="33" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="29" t="inlineStr">
+        <is>
+          <t>Роль</t>
+        </is>
+      </c>
+      <c r="B21" s="29" t="inlineStr">
+        <is>
+          <t>Ключевой тезис</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Аналитик</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Регуляторный риск двойной и по разным законам: 152-ФЗ/ст.13.11 КоАП — про ФИО, снимается маскированием; ФЗ «О рынке ценных бумаг» ст. 3.1 (и потенциально ст. 183 УК РФ при разглашении сотрудником) — про коммерческую/профессиональную тайну брокера, и он НЕ снимается маскированием ФИО. Это два независимых правовых режима.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Архитектор</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Технически «маскировать только название своей компании» сложнее, чем кажется: единственный подходящий regex слоя 1 — общий шаблон «ОПФ + название в кавычках», который одинаково сработает и на «АО «Инвестиционная компания Д8»» в шапке, и на «БПИФ «Т-Капитал…»» в портфеле. Нужна не общая ORG-эвристика, а точечная каталожная аннотация именно на юрлицо заказчика.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Критик</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Вопрос «утечка или нет» (да/нет) сам по себе — ловушка: правильная рамка не бинарная, а «какой остаточный риск и приемлем ли он для этого канала (лог провайдера модели, инсайдер) и класса данных». Также: у платформы, по всей видимости, нет функции обобщения чисел (диапазоны/округление) — только детектирование-и-редактирование сущностей, поэтому «спрятать точные цифры, сохранив аналитическую пользу» может быть architekturно нечем делать без доработки продукта.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="32" t="inlineStr">
+        <is>
+          <t>РЕКОМЕНДАЦИИ (по приоритету)</t>
+        </is>
+      </c>
+      <c r="B26" s="33" t="n"/>
+      <c r="C26" s="33" t="n"/>
+      <c r="D26" s="33" t="n"/>
+      <c r="E26" s="33" t="n"/>
+      <c r="F26" s="33" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="29" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B27" s="29" t="inlineStr">
+        <is>
+          <t>Рекомендация</t>
+        </is>
+      </c>
+      <c r="C27" s="29" t="inlineStr">
+        <is>
+          <t>Почему в этом приоритете</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Маскировать/токенизировать номер договора и номера счетов вместе с ФИО (кастомный тип, уже предложен на листе «Три слоя маскирования»)</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Самое дешёвое действие с наибольшим эффектом: разрывает cross-document join-ключ. Бизнес-конфликта нет — этот буквенно-цифровой номер аналитику для анализа портфеля не нужен</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Добавить номер лицензии и юридический адрес брокера в область детектирования</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Без этого маскирование строки с названием компании не имеет смысла — компания вычисляется по лицензии за секунды через реестр ЦБ РФ</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Для точного состава портфеля/остатков — не бинарное решение «скрыть/не скрыть», а обобщение (диапазоны, округление) ИЛИ компенсирующий контрактный контроль (гарантия провайдера модели не сохранять/не обучаться на данных)</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Платформа сегодня умеет только детектировать-и-редактировать сущности, не обобщать числа — если бизнесу нужны точные цифры, нужен либо запрос новой функции у вендора, либо контрактная мера вместо технической</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Явно протестировать на этом документе: маскируется ли ФИО по ключу «Клиент:» (не только «ФИО:»), и захватывает ли текущая конфигурация ФИО сотрудников-подписантов, а не только клиента</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Оба сценария — реалистичный риск неправильной конфигурации, а не гипотетический; легко проверяется прогоном этого же документа через Журнал LLM-сессий</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Запросить у вендора явное подтверждение: поддерживает ли DLP-механизм (§5.3) блокировку документа целиком по булеву правилу «номер счёта/договора + таблица активов вместе → блок», и завести как отдельный тестовый сценарий пилота</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Архитектурно самое надёжное решение (блокировка документа, а не заплатки по отдельным полям), но сегодня не подтверждено RFI — не считать имеющимся по умолчанию</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Уточнить у заказчика: форма отчёта — единый регуляторный шаблон ЦБ РФ (используется многими брокерами) или специфична для ПО именно Д8?</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>От ответа зависит, имеет ли смысл вообще маскировать название компании в шапке отдельно от лицензии — роли разошлись в оценке этого риска, вопрос открытый</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="46" customHeight="1">
+      <c r="A36" s="26" t="inlineStr">
+        <is>
+          <t>Как читать этот лист: это запись обсуждения (вопрос → анализ трёх независимых ролей → сведённый вердикт), а не готовая функциональная спецификация. Рекомендации 1–2 технически реализуемы уже сейчас через тот же механизм, что и остальные кастомные типы на листе «Три слоя маскирования». Рекомендации 3 и 5 требуют подтверждения возможностей платформы вендором, прежде чем на них полагаться.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/analysis/pokrytie-maskirovaniya-perechen-d8.xlsx
+++ b/docs/analysis/pokrytie-maskirovaniya-perechen-d8.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Три слоя маскирования" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Частичное маскирование" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Стратегия без утечки" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -234,7 +235,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -325,6 +326,17 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3787,11 +3799,6 @@
           <t>ДОКУМЕНТ-ПРИМЕР (расшифровано со скриншота заказчика)</t>
         </is>
       </c>
-      <c r="B4" s="33" t="n"/>
-      <c r="C4" s="33" t="n"/>
-      <c r="D4" s="33" t="n"/>
-      <c r="E4" s="33" t="n"/>
-      <c r="F4" s="33" t="n"/>
     </row>
     <row r="5" ht="62" customHeight="1">
       <c r="A5" s="34" t="inlineStr">
@@ -3806,11 +3813,6 @@
           <t>ВЕРДИКТ</t>
         </is>
       </c>
-      <c r="B7" s="36" t="n"/>
-      <c r="C7" s="36" t="n"/>
-      <c r="D7" s="36" t="n"/>
-      <c r="E7" s="36" t="n"/>
-      <c r="F7" s="36" t="n"/>
     </row>
     <row r="8" ht="62" customHeight="1">
       <c r="A8" s="37" t="inlineStr">
@@ -3818,11 +3820,6 @@
           <t>ДА — предложенная стратегия («скрыть только ФИО + название компании») концептуально ЯВЛЯЕТСЯ утечкой. Единогласный вывод всех трёх ролей. Причина не в том, что маскирование PII работает плохо, а в том, что оно решает не ту задачу: большая часть чувствительного в этом документе — не персональные данные (регулируются 152-ФЗ), а профессиональная/коммерческая тайна брокера (регулируется ФЗ «О рынке ценных бумаг», ст. 3.1, и собственным Перечнем коммерческой тайны заказчика — см. лист «Покрытие маскирования»). «Не ПДн» ≠ «не тайна»: номер договора, номера счетов, состав портфеля и остатки прямо названы в Перечне заказчика (п. 1.3) и уже задокументированы там статусом «Не маскируется».</t>
         </is>
       </c>
-      <c r="B8" s="36" t="n"/>
-      <c r="C8" s="36" t="n"/>
-      <c r="D8" s="36" t="n"/>
-      <c r="E8" s="36" t="n"/>
-      <c r="F8" s="36" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="32" t="inlineStr">
@@ -3830,11 +3827,6 @@
           <t>ЧТО ДЕМАСКИРУЕТ КЛИЕНТА/КОМПАНИЮ ВОПРЕКИ СТРАТЕГИИ</t>
         </is>
       </c>
-      <c r="B10" s="33" t="n"/>
-      <c r="C10" s="33" t="n"/>
-      <c r="D10" s="33" t="n"/>
-      <c r="E10" s="33" t="n"/>
-      <c r="F10" s="33" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="29" t="inlineStr">
@@ -4018,11 +4010,6 @@
           <t>КЛЮЧЕВЫЕ ТЕЗИСЫ ПО РОЛЯМ</t>
         </is>
       </c>
-      <c r="B20" s="33" t="n"/>
-      <c r="C20" s="33" t="n"/>
-      <c r="D20" s="33" t="n"/>
-      <c r="E20" s="33" t="n"/>
-      <c r="F20" s="33" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="29" t="inlineStr">
@@ -4078,11 +4065,6 @@
           <t>РЕКОМЕНДАЦИИ (по приоритету)</t>
         </is>
       </c>
-      <c r="B26" s="33" t="n"/>
-      <c r="C26" s="33" t="n"/>
-      <c r="D26" s="33" t="n"/>
-      <c r="E26" s="33" t="n"/>
-      <c r="F26" s="33" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="29" t="inlineStr">
@@ -4218,11 +4200,608 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A4:F4"/>
     <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A4:F4"/>
     <mergeCell ref="A20:F20"/>
     <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="66" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Пересмотренная стратегия: как закрыть утечку по документу «Отчёт брокера»</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="62" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Продолжение листа «Частичное маскирование» (там — диагноз: стратегия «скрыть только ФИО + название компании» признана утечкой всеми тремя ролями). Здесь — конкретная схема, закрывающая каждую найденную дыру. Ключевое архитектурное решение: не пытаться одной настройкой одновременно защитить данные И сохранить их точность для внешней модели — это невозможно без утраты либо того, либо другого. Вместо этого документ разводится по двум каналам (см. ниже), и только один из них требует компромисса.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="32" t="inlineStr">
+        <is>
+          <t>ГЛАВНОЕ РЕШЕНИЕ: МАРШРУТИЗАЦИЯ ПО КАНАЛУ, А НЕ ЕДИНАЯ НАСТРОЙКА МАСКИРОВАНИЯ</t>
+        </is>
+      </c>
+      <c r="B4" s="33" t="n"/>
+      <c r="C4" s="33" t="n"/>
+      <c r="D4" s="33" t="n"/>
+      <c r="E4" s="33" t="n"/>
+      <c r="F4" s="33" t="n"/>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>Платформа поддерживает разную политику маскирования по поставщику модели (RFI, маршрут данных, шаг 6: «для локальной модели замещение может быть отключено, для внешней — принудительно»). Это даёт естественное решение конфликта «нужны точные цифры для анализа» vs «нельзя отправлять их наружу»:</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>Канал</t>
+        </is>
+      </c>
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>Что разрешено</t>
+        </is>
+      </c>
+      <c r="C6" s="29" t="inlineStr">
+        <is>
+          <t>Почему это закрывает утечку</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>А. Внутренняя модель (GigaChat/Qwen локально, в контуре)</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Полный документ без ограничений — точные цифры портфеля, остатки, номер договора, всё как есть</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Данные физически не покидают периметр заказчика — режим соответствует определению «внутри контура» из Перечня коммерческой тайны (утечка — это именно выход данных вовне, RFI подтверждает, что маскирование для локальной модели может быть отключено)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Б. Внешняя модель (OpenAI/Anthropic и т.п. через veai)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Только после полного маскирования по расширённому списку полей ниже; если документ содержит одновременно счёт/договор и таблицу портфеля — блокировка целиком, а не точечное маскирование (документ-уровневая DLP-политика, см. ниже)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Единственный канал, где данные физически уходят за периметр — здесь и нужна вся тяжесть защиты; для аналитики, которой нужны точные цифры, канал Б просто не подходит по определению — для неё канал А</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>РАСШИРЕННЫЙ СПИСОК МАСКИРУЕМЫХ ПОЛЕЙ — ДЛЯ КАНАЛА Б (ВНЕШНЯЯ МОДЕЛЬ)</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="n"/>
+      <c r="C10" s="33" t="n"/>
+      <c r="D10" s="33" t="n"/>
+      <c r="E10" s="33" t="n"/>
+      <c r="F10" s="33" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>Поле</t>
+        </is>
+      </c>
+      <c r="B11" s="29" t="inlineStr">
+        <is>
+          <t>Было в старой стратегии</t>
+        </is>
+      </c>
+      <c r="C11" s="29" t="inlineStr">
+        <is>
+          <t>Новая мера</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>ФИО клиента</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Маскировалось (по ключу «ФИО:»)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Расширить regex слоя 1: добавить ключ «Клиент:» рядом с «ФИО:» — в реальном документе используется именно эта формулировка, старый шаблон её не ловил</t>
+        </is>
+      </c>
+      <c r="D12" s="38" t="inlineStr">
+        <is>
+          <t>Требует подтверждения вендора</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>ФИО сотрудников (подписи)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Не маскировалось — правило было привязано к полю клиента</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Перенастроить правило на «любая PERSON-сущность в документе», а не только клиентское поле — покрывает подписантов автоматически</t>
+        </is>
+      </c>
+      <c r="D13" s="38" t="inlineStr">
+        <is>
+          <t>Требует подтверждения вендора</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Название компании-брокера</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Маскировалось общим ORG-правилом (риск зацепить и название фонда в портфеле)</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Каталожная аннотация на конкретное юрлицо заказчика, а не общий шаблон «ОПФ + кавычки» — не трогает названия бумаг/фондов в портфеле</t>
+        </is>
+      </c>
+      <c r="D14" s="39" t="inlineStr">
+        <is>
+          <t>Предложение — реализуемо</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Номер лицензии брокера</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>НЕ маскировалось</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Новый кастомный тип «LICENSE_NO» (regex по формату номера лицензии проф. участника РЦБ)</t>
+        </is>
+      </c>
+      <c r="D15" s="39" t="inlineStr">
+        <is>
+          <t>Предложение — реализуемо</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Юридический адрес брокера</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>НЕ маскировалось</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Маскировать точный адрес (дом/район), либо заменить общим «г. Москва» без детализации</t>
+        </is>
+      </c>
+      <c r="D16" s="39" t="inlineStr">
+        <is>
+          <t>Предложение — реализуемо</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Номер договора / брокерский счёт / лицевой счёт</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>НЕ маскировалось — известный пробел (лист «Покрытие маскирования», п. 1.3)</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Кастомный тип «ACCOUNT_ID» (уже предложен на листе «Три слоя маскирования», слой 1) — токенизация с сохранением консистентности: один и тот же номер → одна и та же метка в пределах документа/сессии, чтобы не потерять связность для анализа</t>
+        </is>
+      </c>
+      <c r="D17" s="39" t="inlineStr">
+        <is>
+          <t>Предложение — реализуемо</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>ISIN ценных бумаг</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Не маскировалось</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Оставить как есть — публичный биржевой идентификатор, не создаёт риска сам по себе (см. лист «Частичное маскирование»)</t>
+        </is>
+      </c>
+      <c r="D18" s="40" t="inlineStr">
+        <is>
+          <t>Подтверждено RFI</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Состав портфеля (кол-во/цены) и остатки</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Не маскировалось</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>См. отдельный разбор ниже — единственное поле без чистого технического решения в канале Б</t>
+        </is>
+      </c>
+      <c r="D19" s="38" t="inlineStr">
+        <is>
+          <t>Требует подтверждения вендора</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="41" t="inlineStr">
+        <is>
+          <t>ПОРТФЕЛЬ И ОСТАТКИ — ЕДИНСТВЕННОЕ ПОЛЕ БЕЗ ЧИСТОГО РЕШЕНИЯ В КАНАЛЕ Б</t>
+        </is>
+      </c>
+      <c r="B21" s="42" t="n"/>
+      <c r="C21" s="42" t="n"/>
+      <c r="D21" s="42" t="n"/>
+      <c r="E21" s="42" t="n"/>
+      <c r="F21" s="42" t="n"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="34" t="inlineStr">
+        <is>
+          <t>Даже после маскирования всех полей выше точный набор количеств бумаг и остатков на конкретную дату сам по себе остаётся квазиидентификатором (см. лист «Частичное маскирование», п. 3 «Аналитик+Архитектор+Критик»). Платформа сегодня не подтверждена как умеющая обобщать числа (диапазоны/округление) — только детектировать-и-редактировать сущности. Три варианта для канала Б, ни один не бесплатный:</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>Вариант</t>
+        </is>
+      </c>
+      <c r="B23" s="29" t="inlineStr">
+        <is>
+          <t>Как работает</t>
+        </is>
+      </c>
+      <c r="C23" s="29" t="inlineStr">
+        <is>
+          <t>Компромисс</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Только канал А (рекомендуется по умолчанию)</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Документы с портфелем/остатками по умолчанию идут только на внутреннюю модель, во внешнюю — не передаются вообще</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Аналитика ограничена возможностями локальной модели (обычно слабее внешних топ-моделей по качеству рассуждений)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Обобщение чисел перед отправкой в канал Б</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Точные количества/суммы заменяются диапазонами («1–5 шт.», «15 000–20 000 руб.») до отправки во внешнюю модель</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Требует новой функции платформы (не подтверждена RFI) либо ручной предобработки документа перед загрузкой — сегодня не готово «из коробки»</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Контрактная компенсирующая мера</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Договор с провайдером внешней модели о неиспользовании данных для обучения и минимальном сроке хранения логов (opt-out), передача точных цифр допускается</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Не техническая, а юридическая защита — снижает вероятность вторичного использования, но не устраняет сам факт выхода точных данных за периметр в момент запроса</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="32" t="inlineStr">
+        <is>
+          <t>ДОКУМЕНТ-УРОВНЕВАЯ DLP-ПОЛИТИКА (ДЛЯ КАНАЛА Б)</t>
+        </is>
+      </c>
+      <c r="B28" s="33" t="n"/>
+      <c r="C28" s="33" t="n"/>
+      <c r="D28" s="33" t="n"/>
+      <c r="E28" s="33" t="n"/>
+      <c r="F28" s="33" t="n"/>
+    </row>
+    <row r="29" ht="76" customHeight="1">
+      <c r="A29" s="34" t="inlineStr">
+        <is>
+          <t>Предлагаемое правило для собственного DLP-механизма платформы (§5.3 RFI — классификация текста + база защищаемых сведений + матрица получателей + блокировка/эскалация): «ЕСЛИ документ содержит одновременно (а) паттерн номера договора/счёта (кастомный тип ACCOUNT_ID) И (б) табличную структуру, характерную для портфеля ценных бумаг (наличие ISIN + количество + цена в одной таблице), ТО заблокировать передачу во внешнюю модель и предложить пользователю канал А (внутренняя модель) либо эскалацию на ручное согласование ИБ». ВАЖНО: булева комбинация двух условий в DLP-правиле — не подтверждена RFI как имеющаяся возможность (см. лист «Частичное маскирование», архитектор). Это техническое задание для уточнения у вендора, а не готовая функция, на которую можно полагаться сегодня.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="35" t="inlineStr">
+        <is>
+          <t>ОСТАТОЧНЫЙ РИСК ПОСЛЕ ВСЕХ МЕР — ЧЕСТНО, БЕЗ ПРИУКРАШИВАНИЯ</t>
+        </is>
+      </c>
+      <c r="B31" s="36" t="n"/>
+      <c r="C31" s="36" t="n"/>
+      <c r="D31" s="36" t="n"/>
+      <c r="E31" s="36" t="n"/>
+      <c r="F31" s="36" t="n"/>
+    </row>
+    <row r="32" ht="70" customHeight="1">
+      <c r="A32" s="37" t="inlineStr">
+        <is>
+          <t>Схема выше сводит риск к практически управляемому уровню, но не к нулю — «нет утечки» в абсолютном смысле недостижимо, если бизнесу всё же нужна точная работа с портфельными данными через внешнюю модель (вариант «обобщение чисел» или «контрактная мера» выше). Честная формулировка для заказчика: риск снижается с «прямая деанонимизация клиента по открытым данным» (текущее состояние) до «остаточный риск при инсайдерской угрозе или редком сценарии корреляции с внешней утечкой» (после внедрения схемы) — это управляемый, а не нулевой уровень. Единственный канал с формально нулевым риском выхода данных — канал А (внутренняя модель), и для класса документов вроде «Отчёт брокера» именно он должен быть путём по умолчанию.</t>
+        </is>
+      </c>
+      <c r="B32" s="36" t="n"/>
+      <c r="C32" s="36" t="n"/>
+      <c r="D32" s="36" t="n"/>
+      <c r="E32" s="36" t="n"/>
+      <c r="F32" s="36" t="n"/>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="32" t="inlineStr">
+        <is>
+          <t>ЧЕК-ЛИСТ ВНЕДРЕНИЯ</t>
+        </is>
+      </c>
+      <c r="B34" s="33" t="n"/>
+      <c r="C34" s="33" t="n"/>
+      <c r="D34" s="33" t="n"/>
+      <c r="E34" s="33" t="n"/>
+      <c r="F34" s="33" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="29" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B35" s="29" t="inlineStr">
+        <is>
+          <t>Шаг</t>
+        </is>
+      </c>
+      <c r="C35" s="29" t="inlineStr">
+        <is>
+          <t>Кто/что подтверждает</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Настроить маршрутизацию по умолчанию: документы с признаками счёта/договора + портфеля — только на внутреннюю модель (канал А)</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Конфигурация платформы, наша команда + ИБ заказчика</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Завести кастомные типы ACCOUNT_ID и LICENSE_NO, расширить regex ФИО ключом «Клиент:», перенастроить правило ФИО на «любая PERSON-сущность»</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Вендор — подтвердить техническую реализуемость кастомных типов и переноса правила</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Настроить каталожную аннотацию на юрлицо заказчика вместо общего ORG-правила для названия компании</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Вендор — уточнить, поддерживается ли точечная аннотация на конкретное юрлицо в каталоге метаданных</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Запросить у вендора: поддерживает ли DLP-механизм (§5.3) булеву комбинацию условий для блокировки документа целиком</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Вендор — прямой вопрос, ответ фиксирует реализуемость документ-уровневой политики выше</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Решить с заказчиком: обобщение чисел (нужна доработка продукта) или контрактная мера с провайдером внешней модели — для случаев, когда канал Б всё же нужен с портфельными данными</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Заказчик — бизнес-решение, не техническое</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Прогнать документ «Отчёт брокера» через Журнал LLM-сессий после настройки — проверить фактическое маскирование каждого поля из таблицы выше, а не полагаться на конфигурацию на бумаге</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Пилотная группа Д8 — та же процедура, что в case-03-instrukciya-proverka-maskirovaniya.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="46" customHeight="1">
+      <c r="A44" s="26" t="inlineStr">
+        <is>
+          <t>Как читать этот лист вместе с «Частичное маскирование»: тот лист отвечает на вопрос «является ли исходная стратегия утечкой» (да) — этот лист отвечает на вопрос «что сделать, чтобы не была» (маршрутизация по каналу + расширенный список полей + документ-уровневая политика + честно признанный остаточный риск для одного нерешённого случая — точных портфельных цифр во внешней модели).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A29:F29"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/analysis/pokrytie-maskirovaniya-perechen-d8.xlsx
+++ b/docs/analysis/pokrytie-maskirovaniya-perechen-d8.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -170,6 +170,12 @@
       <color rgb="00A8393B"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="005A3E85"/>
+      <sz val="12"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -235,7 +241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -337,6 +343,7 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2369,7 +2376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3748,13 +3755,205 @@
         </is>
       </c>
     </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="43" t="inlineStr">
+        <is>
+          <t>РАЗДЕЛ 4 — Предлагаемые конфиги CustomPIIType для незакрытых пунктов (п. 1.3, 3.3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="76" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Источник механизма: docs/sources/pii-shield-masking-span-registry.docx, §2 «Кастомные типы (CustomPIIType)» — новый тип маскирования добавляется БЕЗ изменения кода платформы, через конфиг / Admin API (pii_shield/config.py:151-200), полями id (slug), prefix (UPPERCASE → токен [PREFIX_N]), display_name, patterns (regex + флаги + min_confidence + опциональный валидатор), enabled. Количество типов не ограничено. Ниже — конкретные предложения по трём типам из Слоя 1 (см. таблицу выше), которые сегодня не входят во встроенные PIIType. Regex взяты из таблицы Слоя 1 этого листа; для всех трёх контрольной суммы нет (валидатор не нужен), поле «Валидатор» оставлено пустым намеренно. min_confidence — предлагаемые стартовые значения, требуют калибровки на реальных документах Д8 в ходе пилота.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="29" t="inlineStr">
+        <is>
+          <t>Пункт Перечня</t>
+        </is>
+      </c>
+      <c r="B60" s="29" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C60" s="29" t="inlineStr">
+        <is>
+          <t>prefix → токен маски</t>
+        </is>
+      </c>
+      <c r="D60" s="29" t="inlineStr">
+        <is>
+          <t>display_name</t>
+        </is>
+      </c>
+      <c r="E60" s="29" t="inlineStr">
+        <is>
+          <t>Regex-паттерн (patterns)</t>
+        </is>
+      </c>
+      <c r="F60" s="29" t="inlineStr">
+        <is>
+          <t>Валидатор</t>
+        </is>
+      </c>
+      <c r="G60" s="29" t="inlineStr">
+        <is>
+          <t>min_confidence (предложение)</t>
+        </is>
+      </c>
+      <c r="H60" s="29" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>contract_num</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>CONTRACT → [CONTRACT_N]</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Номер договора Д8</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>№?\s?[А-ЯA-Z]{2,10}(?:[\-/][A-Za-zА-я0-9]+){1,5}</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Открытый вопрос заказчику: подтвердить формат номеров договоров по всем подразделениям — regex построен по единственному примеру из Перечня (ИКД-1-PRO-TEST-001), реальная вариативность формата не подтверждена</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>client_code</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>CL → [CL_N]</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Уникальный код клиента</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>CL[\-_]?\d{4,8}</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>Открытый вопрос заказчику: формат гипотетический (CL-000482), реальный шаблон кода клиента у заказчика не подтверждён</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>internal_hostname</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>HOSTNAME → [HOSTNAME_N]</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Внутренний хостнейм</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>[a-z0-9]([a-z0-9\-]{0,61}[a-z0-9])?\.(?:local|internal|corp)\b</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Открытый вопрос заказчику: подтвердить домен(ы) внутренней сети — .local/.internal/.corp здесь заглушка; более узкий min_confidence из-за риска ловить произвольные слова с точкой</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="32" customHeight="1">
+      <c r="A65" s="26" t="inlineStr">
+        <is>
+          <t>Все три — «Низкая» надёжность в Слое 1 выше именно по этой причине: включение в enabled=true до подтверждения формата заказчиком создаёт риск ложных срабатываний. Рекомендация: включать по одному, с проверкой на реальных документах пилота, а не все три сразу.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="12">
     <mergeCell ref="A29:I29"/>
+    <mergeCell ref="A59:I59"/>
+    <mergeCell ref="A65:I65"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A56:I56"/>
     <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A58:I58"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="A20:I20"/>
     <mergeCell ref="A21:I21"/>
@@ -4244,11 +4443,6 @@
           <t>ГЛАВНОЕ РЕШЕНИЕ: МАРШРУТИЗАЦИЯ ПО КАНАЛУ, А НЕ ЕДИНАЯ НАСТРОЙКА МАСКИРОВАНИЯ</t>
         </is>
       </c>
-      <c r="B4" s="33" t="n"/>
-      <c r="C4" s="33" t="n"/>
-      <c r="D4" s="33" t="n"/>
-      <c r="E4" s="33" t="n"/>
-      <c r="F4" s="33" t="n"/>
     </row>
     <row r="5" ht="46" customHeight="1">
       <c r="A5" s="34" t="inlineStr">
@@ -4314,11 +4508,6 @@
           <t>РАСШИРЕННЫЙ СПИСОК МАСКИРУЕМЫХ ПОЛЕЙ — ДЛЯ КАНАЛА Б (ВНЕШНЯЯ МОДЕЛЬ)</t>
         </is>
       </c>
-      <c r="B10" s="33" t="n"/>
-      <c r="C10" s="33" t="n"/>
-      <c r="D10" s="33" t="n"/>
-      <c r="E10" s="33" t="n"/>
-      <c r="F10" s="33" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="29" t="inlineStr">
@@ -4524,11 +4713,6 @@
           <t>ПОРТФЕЛЬ И ОСТАТКИ — ЕДИНСТВЕННОЕ ПОЛЕ БЕЗ ЧИСТОГО РЕШЕНИЯ В КАНАЛЕ Б</t>
         </is>
       </c>
-      <c r="B21" s="42" t="n"/>
-      <c r="C21" s="42" t="n"/>
-      <c r="D21" s="42" t="n"/>
-      <c r="E21" s="42" t="n"/>
-      <c r="F21" s="42" t="n"/>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="34" t="inlineStr">
@@ -4611,11 +4795,6 @@
           <t>ДОКУМЕНТ-УРОВНЕВАЯ DLP-ПОЛИТИКА (ДЛЯ КАНАЛА Б)</t>
         </is>
       </c>
-      <c r="B28" s="33" t="n"/>
-      <c r="C28" s="33" t="n"/>
-      <c r="D28" s="33" t="n"/>
-      <c r="E28" s="33" t="n"/>
-      <c r="F28" s="33" t="n"/>
     </row>
     <row r="29" ht="76" customHeight="1">
       <c r="A29" s="34" t="inlineStr">
@@ -4630,11 +4809,6 @@
           <t>ОСТАТОЧНЫЙ РИСК ПОСЛЕ ВСЕХ МЕР — ЧЕСТНО, БЕЗ ПРИУКРАШИВАНИЯ</t>
         </is>
       </c>
-      <c r="B31" s="36" t="n"/>
-      <c r="C31" s="36" t="n"/>
-      <c r="D31" s="36" t="n"/>
-      <c r="E31" s="36" t="n"/>
-      <c r="F31" s="36" t="n"/>
     </row>
     <row r="32" ht="70" customHeight="1">
       <c r="A32" s="37" t="inlineStr">
@@ -4642,11 +4816,6 @@
           <t>Схема выше сводит риск к практически управляемому уровню, но не к нулю — «нет утечки» в абсолютном смысле недостижимо, если бизнесу всё же нужна точная работа с портфельными данными через внешнюю модель (вариант «обобщение чисел» или «контрактная мера» выше). Честная формулировка для заказчика: риск снижается с «прямая деанонимизация клиента по открытым данным» (текущее состояние) до «остаточный риск при инсайдерской угрозе или редком сценарии корреляции с внешней утечкой» (после внедрения схемы) — это управляемый, а не нулевой уровень. Единственный канал с формально нулевым риском выхода данных — канал А (внутренняя модель), и для класса документов вроде «Отчёт брокера» именно он должен быть путём по умолчанию.</t>
         </is>
       </c>
-      <c r="B32" s="36" t="n"/>
-      <c r="C32" s="36" t="n"/>
-      <c r="D32" s="36" t="n"/>
-      <c r="E32" s="36" t="n"/>
-      <c r="F32" s="36" t="n"/>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="32" t="inlineStr">
@@ -4654,11 +4823,6 @@
           <t>ЧЕК-ЛИСТ ВНЕДРЕНИЯ</t>
         </is>
       </c>
-      <c r="B34" s="33" t="n"/>
-      <c r="C34" s="33" t="n"/>
-      <c r="D34" s="33" t="n"/>
-      <c r="E34" s="33" t="n"/>
-      <c r="F34" s="33" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="29" t="inlineStr">
